--- a/校园招聘/制造业/制造业通用/技术研发类/自动化工程师/3_需重新出题/3轮_制造业通用_自动化工程师_需要重新出题.xlsx
+++ b/校园招聘/制造业/制造业通用/技术研发类/自动化工程师/3_需重新出题/3轮_制造业通用_自动化工程师_需要重新出题.xlsx
@@ -413,86 +413,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>问题</t>
+          <t>技能分类</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>第一层</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>第二层</t>
+          <t>知识点</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>第三层</t>
+          <t>难度</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>技能分类</t>
+          <t>行业</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>岗位</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>知识点</t>
+          <t>招聘场景</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>难度</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>行业</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>岗位</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>招聘场景</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>JD</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
         <is>
           <t>提示词</t>
         </is>
@@ -501,4847 +466,3317 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>某汽车零部件装配线需按节拍自动执行上料、定位、压装、检测、下料五个工序，其中压装工序存在力值超限需紧急回退的可能，且检测结果不合格时要触发返工分支。请简述如何设计状态机来统一管理主流程、异常处理与返工路径，重点说明状态划分依据、不同异常事件下的迁移逻辑，以及如何避免状态爆炸。</t>
+          <t>电气控制</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>状态划分应以工艺动作边界为依据，划分为上料准备、上料执行、定位中、压装中、压装监控、检测中、合格下料、返工启动、返工执行、复检中十个核心状态；迁移逻辑由设备信号和工艺条件共同驱动，如压装中收到力超限信号立即迁入压装监控状态并执行回退动作；通过将异常响应动作封装为可复用的子状态组，而非为每种异常单独设新状态，防止状态数量失控。</t>
+          <t>PLC程序设计</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>常见方案有三种：一是扁平化单层状态机，所有状态平级排列，优点是逻辑透明易调试，但异常分支多时状态数激增；二是分层状态机，主流程与异常处理分属不同层级，异常发生时进入子状态并自动返回上级，兼顾清晰性与可扩展性；三是事件驱动型状态机，用统一事件总线触发迁移，状态间解耦强，但对PLC扫描周期和事件时序要求高。综合产线实时性、维护便利性和工程师实操习惯，分层状态机最适用。</t>
+          <t>状态机设计</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1个异常情况概要：压装过程中力值突变超限但传感器信号抖动导致误判；具体情况：现场振动引发力传感器瞬时尖峰，PLC在一个扫描周期内采样到虚假超限值，触发非必要回退；解决思路：在压装监控状态中嵌入带时间窗的滤波判断，连续两个周期确认超限才执行回退，同时保留急停硬线优先权。1个复杂问题概要：返工路径与主流程共用部分工位资源引发冲突；具体问题：返工时需再次使用定位机构，但主流程已进入下一循环的上料阶段；解决思路：在状态机中增设资源仲裁模块，用互斥标志位协调工位占用权，返工请求必须等待定位机构空闲且当前主流程未锁定该资源后方可进入返工执行状态。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>电气控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PLC程序设计</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>状态机设计</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>加减速曲线如何影响电机驱动的负载冲击？请简单说说。</t>
+          <t>PLC与运动控制</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>加减速曲线决定了电机速度变化的快慢和方式。如果加减速太陡，比如用直线型或未平滑处理的斜坡，电机输出扭矩会突变，导致机械连接件受力骤增，引发负载端的振动、异响甚至松动；如果曲线平缓且连续可导，比如S型或带加加速度限制的曲线，就能让扭矩变化更柔和，显著降低对机械结构的瞬时冲击。</t>
+          <t>运动控制</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>在产线调试中，我们常用三种曲线：一是梯形斜坡，设置简单但启停冲击明显，适合低精度传送带；二是带拐点的双S型，兼顾响应与平稳性，适用于多轴协同的装配工位；三是支持 jerk 限幅的高阶平滑曲线，对伺服驱动器和PLC运算能力要求高，但能有效抑制谐振，常用于高动态定位场景。综合来看，双S型曲线最常用——它不需要高端控制器，又比梯形曲线大幅改善冲击，现场调试周期短、故障率低，是产线快速投产的首选。</t>
+          <t>加减速曲线的作用</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1个异常情况概要：设备运行中出现周期性异响或螺栓松动。具体情况：某包装机推杆机构在高速启停后，连接法兰螺栓两周内多次松脱。解决思路：先用示波器抓取伺服实际电流波形，确认是否存在扭矩尖峰；再检查PLC中加减速时间参数是否被误设为固定值而未随速度段动态调整；最后将原梯形曲线改为双S型，并启用驱动器内置的机械柔顺补偿功能。1个复杂问题概要：多轴同步运动时单轴突发抖动。具体问题：视觉引导的搬运机器人在轨迹末端减速阶段，Z轴出现微幅高频抖动，影响抓取精度。解决思路：排查是否因各轴加减速曲线类型不一致导致惯量耦合失配；统一采用带jerk限幅的S型曲线，并在PLC运动控制模块中启用轴间电子齿轮的动态刚度补偿功能。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PLC与运动控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>运动控制</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>加减速曲线的作用</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>请简单说说编码器在伺服控制回路中提供的是哪一类实时信息？</t>
+          <t>PLC与运动控制</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>编码器在伺服控制回路中提供的是电机轴的实际位置和实际转速这两类实时反馈信息。</t>
+          <t>伺服控制</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>在产线调试和设备维护中，工程师通常会根据现场条件选择三类主流反馈方式：一是增量式编码器，成本低、抗干扰强，但断电后丢失位置，需每次上电回零；二是多圈绝对值编码器，断电不丢位置，省去回零步骤，适合频繁启停的装配工位；三是带单圈绝对值+电池或超级电容保持的多圈编码器，兼顾可靠性与免维护性，是当前新装设备的主流选择。综合来看，在制造业产线长期稳定运行场景下，带非易失性记忆的多圈绝对值编码器最适用——它既避免了回零导致的节拍损失，又减少了因位置丢失引发的撞机风险，时效性和鲁棒性平衡最好。</t>
+          <t>编码器反馈作用</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1个异常情况概要：编码器信号突变导致伺服报警停机。具体情况：产线运行中伺服突然报‘位置偏差超限’，示波器测得A/B相信号出现毛刺或相位跳变，多由机械振动传导至编码器轴、电缆屏蔽层破损或动力线与编码器线并行过长引起。解决思路：先隔离干扰源，检查编码器安装刚性及走线分离距离；再验证屏蔽层单点接地是否规范；最后在PLC侧启用伺服驱动器的位置偏差滤波功能，而非直接调高报警阈值。1个复杂问题概要：多轴协同运动中出现微小同步误差累积。具体问题：在包装机推杆与输送带联动时，连续运行8小时后定位偏移0.15毫米，超出工艺允许公差。解决思路：不是单纯校准编码器零点，而是结合PLC运动控制模块的电子齿轮补偿功能，对主从轴间的传动比漂移进行周期性在线修正，并将修正参数存入伺服驱动器的非易失存储区，确保重启后仍保持同步精度。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PLC与运动控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>伺服控制</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>编码器反馈作用</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>请简单说说，当两个接触器需要防止同时吸合时，电气互锁依靠什么物理特性实现强制约束。</t>
+          <t>电气控制基础</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>电气互锁依靠接触器自身常闭辅助触点的机械联动特性实现强制约束——当一个接触器线圈得电吸合时，其常闭辅助触点必然断开，从而切断另一个接触器的控制回路供电，从物理上阻止后者通电吸合。</t>
+          <t>电气原理识读</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>实际工程中常用三种互锁方式：一是纯硬件电气互锁，即用对方接触器的常闭触点串入本方启动回路，响应快、无延迟、符合功能安全要求，但布线复杂、扩展性差；二是PLC软互锁，在程序里用逻辑互锁标志位控制输出，灵活易修改，但依赖扫描周期和程序执行可靠性，存在微秒级失效窗口；三是硬软双重互锁，既保留常闭触点硬件断路，又在PLC中做状态校验与输出抑制，兼顾安全性和可维护性，是当前产线主流做法。综合来看，双重互锁最稳妥，既满足IEC 61800-5-2对驱动类设备的基本安全要求，又适配自动化工程师日常调试与故障排查的工作节奏。</t>
+          <t>电气互锁原理</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1个异常情况概要：接触器辅助触点粘连失效。具体情况：长期大电流操作导致常闭触点烧蚀熔焊，失去分断能力，使互锁回路形同虚设。解决思路：定期点检触点状态，结合运行次数与负载类型设定预防性更换周期，并在控制柜加装触点状态反馈监测模块，实时比对主触点与辅助触点动作一致性。1个复杂问题概要：多台设备共用同一组互锁信号时的耦合冲突。具体问题：一条输送线含三段驱动，两两之间需正反转互锁，但传统点对点接线造成触点资源紧张、逻辑交叉难追溯。解决思路：采用分布式I/O模块统一采集各接触器状态，由本地PLC按工艺逻辑动态生成互锁使能信号，既减少硬接线，又支持后续产线柔性调整。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>电气控制基础</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>电气原理识读</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>电气互锁原理</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>某产线设备集成项目中，主站通过Modbus RTU同时轮询多个从站，其中一台温控仪表在接收功能码0x10写多个寄存器后，偶发返回0x03非法数据地址响应，但该仪表对功能码0x06写单个寄存器始终成功。请简述你将如何结合功能码0x10的地址范围校验逻辑、从站寄存器映射实际物理布局，以及批量写入时地址连续性与内存分页边界的关系，定位该异常是源于主站地址计算偏差还是从站固件对跨页写入的支持缺陷。</t>
+          <t>工业通信与数据集成</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>功能码0x10要求主站一次性写入的寄存器地址必须连续且全部落在从站合法寄存器范围内；从站收到请求后，会校验起始地址加数量是否越界，并检查该地址段是否全部映射到可写物理存储区域；若涉及跨内存页写入，部分老旧或轻量级固件可能未实现页内校验或页间跳转，导致仅部分地址被识别为非法。</t>
+          <t>Modbus通信应用</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>我会先用串口调试工具抓取异常帧，比对主站发出的起始地址和寄存器数量是否与温控仪表手册标称的可写区一致；再查仪表内部寄存器映射表，确认目标地址段是否横跨两个物理存储页；同时用功能码0x03读取相邻地址验证连续性，排除地址偏移误配；最后在相同条件下用标准Modbus测试主站软件重发请求，交叉验证是否复现。前两种方法时效快但依赖文档准确性，第三种实测最可靠，推荐作为首选验证路径。</t>
+          <t>功能码识别</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1个异常情况概要：主站配置地址偏移量错误。具体情况：工程师按仪表标签地址+1填写，但手册实际采用0基址映射，导致0x10请求首地址整体偏高。解决思路：核对仪表说明书中的地址索引方式，统一主站组态与设备原始定义。1个复杂问题概要：温控仪表固件对跨页批量写支持不完整。具体问题：当写入地址跨越4096寄存器页边界时，固件仅校验首地址页内有效性，忽略后续页权限。解决思路：将大块写操作拆分为页内连续小批次，或联系厂商升级固件补丁。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>工业通信与数据集成</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Modbus通信应用</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>功能码识别</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>请简述，在工业以太网通信中，IP地址冲突主要影响哪一层的数据传输可靠性？</t>
+          <t>工业通信</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IP地址冲突直接影响网络层的数据传输可靠性。因为工业以太网设备依靠IP地址在不同子网或同网段内完成逻辑寻址和路由转发，当两个设备使用相同IP时，网络层无法准确识别目标节点，导致报文误发、丢包或通信中断。</t>
+          <t>通信异常诊断</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>现场常用三种排查与应对方法：一是手动核查并重配IP，优点是无需额外工具，但耗时长、易漏检；二是用便携式网络扫描仪实时发现冲突设备，响应快、覆盖全，但需额外采购且依赖人员操作经验；三是启用交换机的ARP检测或DHCP Snooping功能，能主动拦截异常ARP响应，适合新建产线，但老旧工业交换机普遍不支持。综合来看，对已投运产线，优先采用扫描仪+人工复核组合方式，兼顾时效性与准确性。</t>
+          <t>网络地址冲突</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1个异常情况概要：PLC与HMI之间偶发断连，重启后短暂恢复。具体情况：二者在同一网段且IP重复，导致ARP表频繁刷新，上位机周期性收不到应答。解决思路：先用扫描工具定位冲突源，再核对设备标签与配置记录，最后锁定非标调试遗留的临时IP并清除。1个复杂问题概要：多台伺服驱动器同时失步报警，但物理接线与拓扑无异常。具体问题：某台未纳入资产台账的调试用笔记本电脑被误设为与主控PLC同IP，持续发送虚假ARP响应，干扰了整个运动控制子网的地址解析。解决思路：在核心交换机端口开启端口安全绑定，后续所有新接入设备必须经IT与自动化联合审批并登记IP，同步更新设备台账。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>工业通信</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>通信异常诊断</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>网络地址冲突</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>当多台自动化控制设备通过同一交换机接入局域网后，其中两台设备无法同时稳定在线，进一步确认它们的IP地址均在手动配置范围内、未启用DHCP，且子网掩码一致，此时应重点排查哪类地址层面的冲突？</t>
+          <t>工业通信</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>应重点排查IP地址冲突，即两台设备被手动配置了完全相同的IPv4地址。</t>
+          <t>通信异常诊断</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>在产线现场快速定位时，常用方法有三种：一是用笔记本电脑逐台ping各设备IP并观察响应稳定性，优点是工具易得、无需额外硬件，但无法区分谁在‘冒用’地址；二是登录交换机查看ARP表和端口MAC地址绑定关系，能直接发现同一IP对应多个MAC，时效性和准确性高，但要求工程师具备基础交换机操作能力；三是用网络扫描工具批量探测活跃IP及对应MAC，覆盖全面，但需提前安装软件且可能受防火墙限制。综合来看，优先采用交换机ARP表核查法，它最贴近自动化工程师日常维护权限和响应节奏。</t>
+          <t>网络地址冲突</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1个异常情况概要：设备间断性掉线且日志无通信错误。具体情况：两台PLC配置了相同IP，导致交换机转发混乱，仅最新上线的一台能短暂通信。解决思路：先隔离其中一台，确认另一台恢复稳定，再逐一核对设备标签与配置记录，修正重复IP。1个复杂问题概要：冲突设备中有一台是老旧HMI，其IP配置界面不显示当前实际地址。具体问题：该HMI断电重启后自动回写出厂默认IP，覆盖人工设置，造成隐蔽性冲突。解决思路：现场需断电状态下检查HMI固件版本及配置保存机制，优先升级固件或改用带配置锁定功能的型号，并在交接清单中强制登记IP占用状态。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>工业通信</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>通信异常诊断</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>网络地址冲突</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>在一条采用PROFINET协议的产线设备网络中，主站与多个从站通信时突发部分从站离线，但主站未报总线故障，且交换机端口状态正常。已知网络启用了IRT同步和DRC冗余机制，请简述你如何判断是物理层、协议层还是配置层的问题，并说明恢复通信的关键操作逻辑。</t>
+          <t>工业通信</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>先看现场现象：主站没报总线故障、交换机端口灯亮且无误码，说明物理链路通，但部分从站失联。这提示问题不在主干供电或光纤中断这类硬性断连，而可能出在设备级连接、协议握手异常或参数设置不匹配上。</t>
+          <t>通信异常诊断</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>我会分三步排查：第一，用主站工程软件在线查看各从站的诊断缓冲区和实时状态，重点看是否出现‘设备未响应’‘同步周期超时’或‘DRC切换失败’等提示——这是协议层最直接的证据；第二，逐台检查离线从站的IP地址、设备名称、设备角色（是否被误设为非IRT从站）及DRC主备标识是否与组态一致，这是配置层的核心验证点；第三，在现场用万用表测从站供电电压、用网线测试仪查RJ45插头接触性，并观察从站指示灯是否显示‘运行但无通信’——这能快速定位物理层末端隐患。三步中，优先做第二步配置核对，因为80%同类问题源于组态未下载或参数错位，耗时短、见效快。</t>
+          <t>通信中断恢复</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1个异常情况概要：从站设备名称或IP地址与主站组态不一致。具体情况：工程师曾修改过某台伺服驱动器的设备名称，但未同步更新主站项目并重新下载。解决思路：在主站软件中导出当前在线设备列表，逐条比对名称和IP，发现不一致项后，修正组态并执行完整下载，严禁仅单台下载。1个复杂问题概要：DRC冗余路径切换后，部分从站因地址冲突或时钟源漂移无法重新接入。具体问题：备用主站接管后，原主站未完全退出，导致双主站同时发同步帧，引发从站通信紊乱。解决思路：确认DRC切换日志，强制复位原主站控制器，再按标准流程执行DRC初始化重同步，过程中全程监控IRT周期抖动值是否回归稳定区间。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>工业通信</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>通信异常诊断</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>通信中断恢复</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>一条工业环网中，新增两台支持LLDP的智能电表后，原有视觉检测站出现间歇性数据中断，抓包显示大量重复ARP应答且TTL异常衰减。请说明如何结合设备上电时序、ARP缓存老化机制与环网拓扑特性，构建冲突判定的因果链，并指出最关键的可观察证据。</t>
+          <t>工业通信</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>新增电表上电时未同步隔离环网端口，导致其LLDP报文触发环网协议重收敛；在此过程中，电表误发自身IP对应的ARP应答，与视觉站已有的ARP缓存条目冲突；而环网拓扑下广播帧被冗余转发，加剧ARP响应泛洪；ARP缓存老化时间固定，但反复收到冲突应答导致缓存频繁刷新或失效，最终使视觉站无法稳定解析网关MAC地址。</t>
+          <t>通信异常诊断</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>有四种常用排查路径：一是逐台断电验证，时效快但无法复现瞬态冲突；二是启用环网管理端口阻塞日志，能定位收敛事件但依赖设备支持；三是抓取全网关键节点的ARP+LLDP+环网状态三类报文并做时序对齐，覆盖全面但需协调多设备权限；四是配置ARP静态绑定加环网端口延迟上电，从源头抑制冲突但需修改部署流程。综合来看，第三种方法最平衡——既不改动现有配置，又能还原真实时序关系，符合自动化工程师在现场快速协同诊断的工作习惯。</t>
+          <t>网络地址冲突</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1个异常情况概要：视觉站ARP缓存条目反复被覆盖。具体情况：抓包中同一IP对应多个不同MAC地址的ARP应答，且时间间隔短于缓存老化周期。解决思路：在视觉站所在交换机端口开启ARP防欺骗功能，并核对电表IP是否与现网规划重复。1个复杂问题概要：环网收敛期间LLDP与ARP行为耦合引发隐蔽冲突。具体问题：电表LLDP通告的管理IP恰好与视觉站网关IP相同，但设备未启用IP冲突检测。解决思路：核查所有新入网设备的管理IP分配台账，强制要求LLDP管理地址独立于业务子网，并在环网控制器中启用LLDP-MAC-IP一致性校验。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>工业通信</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>通信异常诊断</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>网络地址冲突</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>在视觉引导的自动锁付工位中，夹治具每次装夹后，机器视觉系统识别的基准标记中心坐标波动极小，标准差低于0.008毫米。请简单说说，这种微小波动反映夹治具在哪个核心定位特性上的稳定性？</t>
+          <t>机械结构与设备机构</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>这反映的是夹治具的重复定位精度。它衡量的是同一夹治具在相同操作条件下，多次装夹同一工件时，其定位基准相对于机床或视觉坐标系所能复现的位置一致性。</t>
+          <t>夹治具定位理解</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>实际工作中，提升重复定位精度主要有四种常用路径：一是采用高刚性、低间隙的机械定位结构，比如带预紧的锥销+平面组合定位，响应快、寿命长，但对加工和装配要求极高；二是使用气动/液压浮动补偿机构，在装夹瞬间吸收微小偏差，适应性好但会引入额外动态响应时间；三是通过伺服压紧力闭环控制稳定夹紧状态，能抑制热变形和弹性变形，但需与PLC运动周期协同；四是结合视觉反馈做二次微调，实时修正位置，精度高但增加系统复杂度和节拍风险。综合来看，在自动锁付这类高节拍、高可靠性场景下，优先选用高刚性机械定位结构为主、辅以压紧力闭环控制，平衡精度、速度与维护性。</t>
+          <t>重复定位精度</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1个异常情况概要：夹治具重复定位精度突然劣化。具体情况：连续多批次检测显示标准差从0.007毫米跳升至0.015毫米以上，且无明显磨损痕迹。解决思路：先排查定位面清洁度与异物嵌入，再检查定位销配合间隙是否因长期振动松动，最后确认夹紧基准面是否存在微观塑性变形。 1个复杂问题概要：不同工件型号共用同一夹治具时重复定位精度不一致。具体问题：A型工件达标，B型工件波动超标，二者仅外形尺寸差异较小。解决思路：重点验证B型工件在夹紧过程中是否引发定位元件微变形或基准面局部悬空，需通过千分表实测各定位点受力变形量，并针对性优化支撑布局或增设辅助定位点。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>机械结构与设备机构</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>夹治具定位理解</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>重复定位精度</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>一台用于精密压装的自动化设备，其夹治具在连续运行8小时、完成300次装夹循环后，压头对准工件定位孔的实际落点仍保持高度集中，极差不超过0.02毫米。请简单说说，该数据主要验证夹治具哪一项与多次操作相关的精度性能？</t>
+          <t>机械结构与设备机构</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>这个数据主要验证的是夹治具的重复定位精度。它反映的是在相同工艺条件下，夹治具对同一工件反复执行定位动作时，每次实际定位位置的一致性程度。</t>
+          <t>夹治具定位理解</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>在自动化产线现场，验证和保障重复定位精度通常有三种主流做法：一是采用高刚性快换定位销配合过盈配合基座，结构简单、响应快，但长期磨损后精度衰减明显；二是使用带预紧补偿的双斜面自定心结构，抗偏载能力强，但装配调试周期较长；三是集成微型位移传感器做闭环反馈，精度稳定性最好，但成本高且需匹配控制系统逻辑。综合产线节拍、维护便利性和长期可靠性，当前主流方案是第二种——即机械式自定心+刚性支撑组合，它在不过度增加调试负担的前提下，最能兼顾量产环境下的精度维持能力。</t>
+          <t>重复定位精度</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1个异常情况概要：夹治具重复定位精度在连续运行中突然变差。具体情况：前200次循环极差稳定在0.015毫米以内，第250次起极差跳增至0.03毫米以上，且无明显异响或卡滞。解决思路：优先排查定位销导向段微划伤或基座安装螺栓轻微松动，用塞尺和扭矩扳手快速复测，不依赖拆解。1个复杂问题概要：同一批夹治具中部分单元达标、部分不达标。具体问题：抽检10套夹治具，仅6套满足300次后极差≤0.02毫米，差异集中在同一加工批次的定位基准面平面度波动。解决思路：回归制造过程，核查精磨工序的夹持变形控制参数与冷却液流量一致性，而非直接返修成品。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>机械结构与设备机构</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>夹治具定位理解</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>重复定位精度</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>当视觉系统完成图像分析后，向控制设备反馈判定结果时，通常采用哪种二值化逻辑表达方式？</t>
+          <t>机器视觉应用</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>在制造业自动化产线中，视觉系统向PLC或运动控制器反馈判定结果时，统一采用‘高电平有效’的开关量信号逻辑：即用通断状态代表‘合格/不合格’或‘通过/不通过’两类明确结论，信号常态为断开（0），判定成功时闭合（1）。</t>
+          <t>视觉系统集成</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>实际工程中主要有三种实现方式：一是通过视觉系统的数字输出端子直连PLC输入点，响应快、接线简洁，但受传输距离和电气干扰影响较大；二是经安全继电器隔离后接入，抗干扰强、符合电气安全规范，适合多台设备共用判定信号的场景；三是通过工业以太网协议映射为布尔变量传输，灵活性高、便于扩展，但需协调通信周期与判定时效性。综合产线稳定性、调试效率和安全合规要求，优先选用带安全隔离的硬接线方式——它既满足毫秒级响应需求，又规避了协议解析延迟和网络单点故障风险。</t>
+          <t>视觉结果判定逻辑</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1个异常情况概要：判定信号偶发误触发。具体情况：视觉系统输出触点在工况振动或电源波动时出现瞬时抖动，导致PLC误读为多次合格信号。解决思路：在PLC端设置不小于20毫秒的硬件滤波或软件消抖，同时核查视觉设备供电回路与动力线路是否共地干扰。1个复杂问题概要：多工位共享同一判定结果时逻辑冲突。具体问题：一条装配线上三个工位需依据同一个视觉判定结果执行不同动作，但部分工位要求延时响应、部分要求立即锁止，硬接线无法分发差异逻辑。解决思路：将原始判定信号作为主控使能条件，由PLC内部按工艺节拍生成分级输出，避免在视觉侧做逻辑拆分，确保判定源头唯一、执行路径可控。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>机器视觉应用</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>视觉系统集成</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>视觉结果判定逻辑</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>在调试过程中，单机调试和联机调试分别依据什么信号来启动设备动作？</t>
+          <t>调试与验收</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>单机调试时，设备动作由本地手动信号启动，比如操作面板上的启动按钮、急停复位信号或示教器发出的点动指令；联机调试时，设备动作由上位系统下发的自动运行指令信号启动，通常是来自产线主控PLC或调度系统的使能与启动脉冲信号。</t>
+          <t>设备调试</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>实际工作中常用三种启动信号方式：一是硬接线方式，通过物理端子接收按钮或继电器信号，响应快但扩展性差；二是基于标准IO映射的软启方式，通过PLC内部标志位触发，配置灵活且便于逻辑隔离；三是总线级协同启动，如通过现场总线同步周期内的启动使能帧触发，适合多轴精密联动。综合来看，IO映射方式在制造业自动化项目中适用性最广——它兼顾调试安全性、逻辑可追溯性和产线集成便利性，既满足单机验证阶段的独立可控要求，又能平滑过渡到联机模式下的信号对齐。</t>
+          <t>单机与联机调试区别</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1个异常情况概要：单机能动、联机不启动。具体情况：设备本地启停正常，但接入产线后收不到启动脉冲，或收到后无响应。解决思路：先确认信号方向与电平匹配性，再检查联机模式下设备是否处于‘就绪等待’状态，最后核对主从站之间的启动使能握手逻辑是否完整执行。1个复杂问题概要：多工位设备在联机调试中出现启停不同步。具体问题：某装配单元的输送、定位、压装三段动作在联机模式下存在毫秒级时序偏差，导致节拍超差或误报警。解决思路：不依赖单一启动信号，而是将启动指令拆解为分阶段使能信号，并在设备侧嵌入轻量级状态机，结合本地传感器反馈动态校准各环节的执行窗口，确保动作链在联机约束下仍保持工艺刚性。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>调试与验收</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>设备调试</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>单机与联机调试区别</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>在完成输送线、分拣机构和扫码站各自的单机调试后，开始联机调试。此时若发现扫码结果无法触发下游分拣动作，应优先检查哪类信号的传递路径？请简述该路径在联机调试中承载的关键功能。</t>
+          <t>调试与验收</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>应优先检查控制信号的传递路径。这条路径在联机调试中承担着将扫码识别结果转化为实际执行指令的核心作用，是连接信息层与执行层的桥梁。</t>
+          <t>设备调试</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>常见方案有三种：一是通过PLC内部软接线实现信号映射，优势是响应快、修改灵活，但依赖程序逻辑完整性；二是采用硬接线方式直接传送开关量信号，优势是可靠性高、故障定位直观，但扩展性差、布线复杂；三是通过工业现场总线统一调度，优势是支持状态反馈与协同时序，但对设备协议一致性要求高。综合时效性、可复现性和现场适配性，优先采用硬接线+PLC软逻辑双重验证的方式——既保证基础触发可靠，又便于快速隔离是信号源问题还是执行逻辑问题。</t>
+          <t>单机与联机调试区别</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1个异常情况概要：扫码信号发出但分拣机构无响应。具体情况：扫码站输出指示灯亮、PLC输入点有电平变化，但分拣动作未启动。解决思路：先确认PLC输出端是否有效驱动执行器，再回溯检查联机模式下是否启用了互锁条件或急停连锁，重点排查安全继电器或模式选择开关的状态。1个复杂问题概要：多工位协同时扫码结果偶发丢失触发。具体问题：仅在高速连续进料时段出现，单机测试全部正常。解决思路：聚焦信号传递路径中的时序裕度，核查输送线到位检测与扫码触发之间的时间窗是否被压缩，同步检查PLC扫描周期与外部信号保持时间是否匹配，并在联机状态下实测关键节点信号的建立与保持时间。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>调试与验收</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>设备调试</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>单机与联机调试区别</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>请简单说说‘故障复现’这一环节，在验收阶段主要验证的是什么？</t>
+          <t>调试与验收</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>在自动化系统验收阶段，‘故障复现’主要验证的是：设备或产线在真实工况下，能否稳定、可重复地表现出客户报称的异常现象；同时确认该现象确由被交付系统自身引发，而非外部干扰或操作误用所致。</t>
+          <t>故障诊断</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>实际工作中常用四种方式：一是按原始报警记录和操作日志回放工况，优势是贴近真实，但依赖日志完整性；二是模拟典型触发条件（如特定速度突变、传感器遮挡、负载阶跃），响应快、可控性强，但可能遗漏隐性耦合因素；三是分段隔离测试——先断开外围设备单独运行PLC逻辑，再逐步接入执行单元，能准确定界，但耗时较长；四是利用调试模式下的强制信号注入，效率高，但存在绕过安全机制风险。综合来看，‘模拟典型触发条件+分段隔离验证’组合最稳妥，既保障时效，又能覆盖软硬协同类问题。</t>
+          <t>故障复现与验证</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1个异常情况概要：复现失败，即按客户描述反复操作却无法再现故障。具体情况：现场环境参数（如温度、电压波动、气压）与故障发生时存在细微差异，或操作节奏、起始状态未完全一致。解决思路：不急于归因‘假故障’，而是协同客户回溯故障发生前3分钟完整动作链，同步采集关键点位信号趋势，锁定隐性触发窗口。1个复杂问题概要：故障仅在多工序连续运行2小时后偶发。具体问题：涉及热积累、通信延迟累积、缓存溢出等时序耦合效应，单次短时测试无法暴露。解决思路：设计加速老化验证流程——在安全前提下提升节拍频率并延长连续运行时长，同步对PLC任务周期、总线响应时间、伺服温升曲线做趋势比对，定位性能衰减拐点。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>调试与验收</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>故障诊断</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>故障复现与验证</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>某气动阀反馈信号在DCS画面上始终显示‘故障’，现场测量阀位传感器输出为10V直流，而IO模块对应通道电压为0V，你如何快速定位是接线松动还是模块通道损坏？请简述排查逻辑。</t>
+          <t>现场联调</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>首先确认信号路径：传感器→现场接线端子→中间过渡端子（如有）→DCS机柜内端子排→IO模块通道输入点。题干中传感器端有10V输出、模块通道测得0V，说明问题一定出现在这两点之间的物理连接环节。</t>
+          <t>设备故障诊断</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>有四种常用排查方式：一是用万用表通断档查端子间导线连通性，快但无法发现接触电阻过大或虚接；二是带电测量各段压降，能发现高阻接点但需注意安全距离；三是分段短接法——从模块侧向现场逐段短接并观察画面变化，时效性好且结果直观；四是更换备用通道做交叉验证，准确但依赖备件。综合来看，优先采用分段短接法，既不依赖备件，又能5分钟内锁定故障段，最契合现场联调对效率与确定性的双重要求。</t>
+          <t>信号链路排查</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1个异常情况概要：端子螺丝看似拧紧，实则压接不牢导致接触电阻突增。具体情况：万用表测通断正常，但加载信号后压降陡升，模块侧电压骤降为0。解决思路：用红外测温仪扫查接线点，发热处即为高阻点；或轻摇导线同时监测模块侧电压，波动即证实虚接。1个复杂问题概要：同一机柜内多路模拟量通道集体异常。具体问题：并非单点故障，而是机柜公共地线松脱或供电纹波超标。解决思路：先测模块供电电压及参考地电位，再对比相邻正常通道的共模电压，确认是否为系统级接地或电源问题，避免误判为单通道损坏。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>现场联调</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>设备故障诊断</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>信号链路排查</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>某自动装配工位的扭矩测量设备已投入试运行，其CPK值为1.2。请简单说说这个数值说明当前过程能力满足产品公差要求的程度，以及它反映的是长期还是短期的稳定表现。</t>
+          <t>调试与验收</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CPK值为1.2，说明该扭矩测量过程在当前试运行阶段基本满足产品公差要求，但余量有限；它反映的是短期过程能力，即在受控、稳定条件下的表现，不包含设备老化、传感器漂移、环境变化等长期因素的影响。</t>
+          <t>精度验证</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>在自动化产线调试与验收环节，验证CPK常用三种方式：一是用新装传感器配合标准扭矩仪做多批次比对测试，时效快但依赖标定精度；二是通过连续采集同一工位30～50个合格零件的实测数据计算，覆盖真实节拍和工况，但需等待足够样本；三是嵌入PLC实时统计模块，在线滚动计算CPK趋势，响应及时但对数据清洗和异常剔除要求高。综合来看，第二种方法最稳妥——既真实反映装配节拍下的测量稳定性，又便于与工艺文件中的公差带直接对标，是验收阶段被广泛采用的基准做法。</t>
+          <t>GRR与CPK含义</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1个异常情况概要：CPK突然从1.2跌至0.8。具体情况：试运行第三天起，连续两批数据出现明显右偏，且极差扩大。解决思路：立即暂停该工位运行，检查扭矩传感器安装是否松动、气动拧紧轴是否存在漏气导致输出波动、以及信号线屏蔽是否失效引入干扰。先复位再单点复测，确认硬件状态后再重采数据。1个复杂问题概要：CPK达标但现场仍频繁出现扭矩超差报警。具体问题：测量系统CPK=1.2，但下游质量抽检发现约3%的螺栓实际松脱。解决思路：排查测量与执行的耦合偏差——重点验证拧紧程序中设定扭矩与传感器反馈值的同步时序、判断窗口是否过短，以及是否因伺服响应滞后导致‘假达标’；需联合调试拧紧控制器与测量模块的触发逻辑，而非仅优化测量本身。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>调试与验收</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>精度验证</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>GRR与CPK含义</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>请简单说说，为什么关键部件的寿命数据通常作为更换或检修的依据？</t>
+          <t>设备诊断改善</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>因为自动化工程师在产线运行中，需要提前识别设备失效风险，而关键部件的寿命数据是经过长期运行验证的、反映其性能退化趋势的客观指标，直接关联到设备功能完整性与产线连续性，所以被用作制定更换或检修决策的核心依据。</t>
+          <t>预防性维护</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>实际工作中常用三种方式：一是基于设备制造商提供的标称寿命值，优点是获取简单、有依据，但未考虑现场工况差异，容易导致过早更换或延误检修；二是结合PLC采集的累计运行时间、启停次数和负载波动数据做动态折算，时效性强、适配产线实际，但需校准不同工况下的衰减权重；三是融合传感器监测的振动、温升等状态特征做趋势外推，覆盖更全面，但对信号质量和算法鲁棒性要求高。综合来看，第二种方式在制造业现场最常用——它不依赖额外硬件投入，能快速落地，且与现有自动化系统深度协同。</t>
+          <t>关键部件寿命</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1个异常情况概要：寿命数据突然大幅偏离预期。具体情况：某伺服电机标称寿命10000小时，但运行6000小时后电流波动突增，寿命折算值骤降至剩余800小时。解决思路：立即核查该时段是否发生过载、急停频次异常或冷却失效，同步调取PLC历史报警与温度记录交叉验证，确认是否为偶发工况扰动而非材料劣化。1个复杂问题概要：多部件耦合失效下单一寿命指标失效。具体问题：输送线张紧轮与同步带寿命不同步，仅按张紧轮寿命更换，同步带却提前断裂引发停机。解决思路：建立部件关联关系表，在MES或CMMS中设置联动维护策略，以‘功能组’为单位统筹寿命阈值，并通过产线级运行日志回溯分析耦合退化规律。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>设备诊断改善</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>预防性维护</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>关键部件寿命</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MTBF数值越高，说明设备在两次故障之间平均能连续运行的时间如何变化？</t>
+          <t>设备诊断改善</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MTBF数值越高，说明设备在两次故障之间平均能连续运行的时间越长。</t>
+          <t>设备可靠性分析</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>在自动化产线日常运维中，提升MTBF主要有四种常用路径：一是通过PLC逻辑优化，屏蔽偶发干扰导致的误停机，响应快但无法改善硬件老化；二是对关键执行部件（如气动阀、光电开关）实施预防性更换周期管理，覆盖全面但需依赖历史故障数据支撑；三是加装边缘侧振动与温升监测模块，实现早期退化识别，时效性强且针对性好，但需匹配现场供电与安装空间；四是重构设备启停逻辑，减少频繁动作带来的机械磨损，见效稳定但需联合工艺部门确认节拍可行性。综合来看，边缘监测加预防性更换组合应用最稳妥，既保障实时性，又兼顾系统性。</t>
+          <t>MTBF指标含义</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1个异常情况概要：MTBF统计值突然升高。具体情况：并非设备变可靠，而是故障漏报或自动复位未被记录，比如伺服驱动器过载后自行恢复、HMI未弹出报警但PLC已触发软复位。解决思路：核查PLC报警日志与HMI事件记录的一致性，校准故障判定逻辑，确保所有非计划停机均被唯一标记并计入统计周期。1个复杂问题概要：同一型号设备在不同产线MTBF差异显著。具体问题：表面看是设备问题，实则由节拍设定、环境温湿度、操作习惯等现场因素叠加导致。解决思路：以单台设备为最小分析单元，同步采集运行时长、启停频次、负载率及环境参数，用归因分析锁定主导影响因子，再针对性调整点检标准或操作指引。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>设备诊断改善</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>设备可靠性分析</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>MTBF指标含义</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>在自动化产线中，技术人员常通过统计设备两次故障之间的运行时长来计算一个平均值。请简单说说，这个平均值主要用来衡量设备在哪一方面的运行表现？</t>
+          <t>设备诊断改善</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>这个平均值主要用来衡量设备的可靠性表现，具体反映的是设备在正常运行状态下，能够持续稳定工作、不发生功能失效的时间水平。</t>
+          <t>设备可靠性分析</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>在实际产线运维中，技术人员常用三种方式获取和应用这个均值：一是基于维修工单记录的手动汇总，优点是数据来源真实、责任可追溯，但存在录入延迟和漏记风险；二是通过PLC内置运行计时器与故障信号联动自动采集，时效性高、连续性强，但依赖信号定义规范性和IO点配置完整性；三是结合边缘网关对多台同类设备运行数据做聚合分析，能识别共性薄弱环节，但需确保设备状态判定逻辑一致。综合来看，第二种方式——即利用PLC本地运行计时与故障触发机制联动采集——在保证时效性的同时兼顾准确性与实施成本，是当前自动化工程师最常采用且最务实的技术路径。</t>
+          <t>MTBF指标含义</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1个异常情况概要：平均值突然显著升高。具体情况：并非设备变可靠了，而是故障报修流程被人为绕过，比如操作工直接复位重启而不提报故障，导致‘无记录停机’未被统计。解决思路：将设备重启动作与MES工单系统强制关联，同时在HMI增设一键报修弹窗，从流程上堵住漏统缺口。1个复杂问题概要：同类设备MTBF差异过大。具体问题：同一型号的五台包装机，其中两台MTBF只有其余三台的一半，但故障代码和维修记录未显示明显规律。解决思路：调取这五台设备近三个月的PLC运行日志，重点比对启停频次、负载波动幅度和急停触发前的运动轨迹一致性，定位是否由上游工位节拍不稳引发的隐性机械疲劳。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>设备诊断改善</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>设备可靠性分析</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>MTBF指标含义</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>当一台数控加工设备在一年内发生6次非人为导致的停机故障，每次故障前的连续运行时间分别为1020、980、1150、1060、990和1100小时，取其平均值作为评估依据。请简单说说，这个平均值所代表的指标，核心反映的是设备哪类性能特征？</t>
+          <t>设备诊断改善</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>这个平均值代表的是设备的平均无故障运行时间，也就是常说的MTBF。它直接刻画的是设备在正常运行状态下，两次非人为故障之间能稳定工作多久，反映的是设备固有的可靠性水平。</t>
+          <t>设备可靠性分析</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>在自动化工程师日常工作中，评估MTBF通常有三种方式：一是基于现场实际故障记录的手动统计，时效快但依赖维修记录完整性；二是通过设备物联网模块自动采集运行与停机状态生成时间序列，覆盖全、精度高，但需确认信号触发逻辑是否准确识别真实故障；三是结合PLC内部运行计时器与报警日志交叉比对，能排除误报干扰，但需要熟悉该机型的逻辑架构。综合来看，第二种方式最常用——既满足产线不停机监测要求，又能在月度可靠性分析中快速输出结果，是当前主流产线部署的标准做法。</t>
+          <t>MTBF指标含义</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1个异常情况概要：MTBF数值看似稳定，但实际故障集中在某类工况下重复发生。具体情况：比如6次故障全部出现在重切削连续加工超过8小时后。解决思路：不单看平均值，要回溯每次故障前的负载曲线、温升趋势和轴向振动数据，锁定工艺窗口与薄弱环节的关联关系。1个复杂问题概要：同一型号多台设备MTBF差异显著。具体问题：A线三台同款机床，MTBF相差超30%，但维修记录和备件更换频次接近。解决思路：重点排查设备安装基础刚性、冷却液清洁度长期累积影响、以及数控系统参数版本是否一致，优先从现场环境与配置一致性入手，而不是直接归因于设备本体质量。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>设备诊断改善</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>设备可靠性分析</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>MTBF指标含义</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>设备运维报告中将‘平均无故障运行时间’列为关键监控项之一，并与备件更换周期、点检频次联动调整。请简单说说，这个指标在日常维护决策中主要支撑哪一类维护策略的合理性判断？</t>
+          <t>设备诊断改善</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>这个指标主要支撑预防性维护策略的合理性判断。它反映设备在两次随机故障之间的稳定运行能力，是评估是否需要提前干预、避免突发停机的核心依据。</t>
+          <t>设备可靠性分析</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>在实际工作中，工程师常基于MTBF数据采用三类调整方式：一是固定周期维护，优点是执行简单，但容易造成过维护或欠维护；二是按运行小时动态触发，更贴合设备真实损耗，但依赖准确的运行时长采集；三是结合历史故障模式做分级预警，比如对MTBF持续下滑的设备缩短点检间隔，兼顾时效与精准。综合来看，第三种方式最常用也最合理——它不单看数值高低，而是关注趋势变化，能及时识别早期劣化，又避免盲目调频影响产线节奏。</t>
+          <t>MTBF指标含义</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1个异常情况概要：MTBF数值短期骤升。具体情况：某条产线PLC记录的故障次数突然减少，导致MTBF虚高，实则因传感器失灵未捕获微小异常，点检频次被误下调。解决思路：同步核查底层信号有效性，用人工点检复核关键节点状态，确认数据可信后再调整策略。1个复杂问题概要：多台同型号设备MTBF差异显著。具体问题：同一车间内五台相同品牌伺服压机，MTBF相差达40%，无法统一制定备件策略。解决思路：分设备拉取运行负载、启停频次、环境温湿度等过程参数，定位差异主因是冷却条件不均，针对性优化散热后重新校准维护周期。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>设备诊断改善</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>设备可靠性分析</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>MTBF指标含义</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>请简述状态机设计中‘状态’和‘转移条件’分别指什么？</t>
+          <t>电气控制</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>在自动化产线的PLC程序设计中，‘状态’指的是设备当前所处的、具有明确工艺意义且持续执行某类动作的运行阶段，比如‘夹紧到位’‘主轴启动中’‘等待扫码完成’；‘转移条件’指的是触发设备从当前状态切换到下一状态所必须满足的、可被PLC实时监测的物理信号或逻辑组合，比如‘气缸到位传感器信号为真且压力值稳定超过2秒’。</t>
+          <t>PLC程序设计</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>实际产线中常用三种实现方式：一是用单个整型寄存器编码状态，优点是内存占用小、调试直观，但扩展性差，新增状态需重编全部编号；二是用布尔型状态位组，每个状态独立置位，便于并行判断和故障隔离，但占用字节多、逻辑易冗余；三是基于结构化文本的枚举+条件块组合，可读性强、支持注释和跳转标记，对新员工友好，且兼容主流PLC平台。综合来看，第三种方式在当前产线升级和跨品牌调试场景下更可靠，既保障逻辑清晰，又避免硬编码导致的维护断层。</t>
+          <t>状态机设计</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1个异常情况概要：状态滞留——具体情况：设备卡在‘送料完成’状态迟迟不进入‘压装启动’，实际是光电开关被油污遮挡导致信号偶发丢失，但PLC未设超时强制退出机制；解决思路：为每个关键状态配置独立的超时监控定时器，超时后自动触发报警并转入安全停机状态，同时记录滞留时长供维修追溯。1个复杂问题概要：多设备协同状态冲突——具体问题：两台机械手共用同一工位时，因各自状态机未共享互锁信号，出现同时向工位伸入手臂的碰撞风险；解决思路：在主控PLC中建立统一的状态仲裁模块，通过全局状态映射表和带优先级的请求-应答机制，确保任一时刻仅允许一个设备获得工位使用权，并同步刷新所有关联设备的状态视图。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>电气控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>PLC程序设计</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>状态机设计</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>一条输送带需要在前方光电开关检测到物料后延时3秒再启动，以避免误触发。请简述在梯形图中如何用定时器指令配合输入信号完成这个延时启动逻辑。</t>
+          <t>电气控制</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>在梯形图中，需将光电开关的常开触点作为定时器的启动条件；当触点闭合时，定时器开始计时；设定定时时间为3秒；定时器到达设定值后，其常开触点闭合，驱动输送带启停输出线圈。</t>
+          <t>PLC程序设计</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>实际工程中常用三种实现方式：第一种是单定时器直接驱动输出，结构最简但无法区分瞬时干扰与真实物料；第二种是采用‘定时器+置位复位’组合，用光电信号启动定时器，定时结束置位输出，再用停止信号或延时后复位，抗干扰强、状态明确；第三种是加入前沿检测，即先用上升沿触发定时器，避免光电抖动重复启动。综合来看，第二种方案最常用——它兼顾了逻辑清晰性、调试便利性和产线维护需求，在设备频繁启停、粉尘环境多的制造现场稳定性最高。</t>
+          <t>梯形图逻辑</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1个异常情况概要：光电开关受粉尘遮挡导致信号反复通断。具体情况：物料未完全通过时，光电被遮挡又短暂透光，引发定时器多次启停，输送带出现抖动启动。解决思路：在输入端增加硬件滤波或软件去抖，梯形图中改用上升沿触发并配合最小有效持续时间判断，确保只有稳定遮挡超200毫秒才启动定时。1个复杂问题概要：多段输送带协同延时启动时，前段延时未完成，后段已收到联动信号。具体问题：相邻工位信号耦合，导致下游输送带提前动作，造成物料堆积或卡滞。解决思路：将延时逻辑封装为带使能和完成标志的标准化功能块，各段间通过完成信号串行连锁，而非依赖原始光电信号，确保时序严格受控。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>电气控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PLC程序设计</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>梯形图逻辑</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>请简述步进流程设计中‘步’的基本含义。</t>
+          <t>PLC控制</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>在PLC顺序控制的步进流程设计中，‘步’指的是设备或产线在一个稳定工况下所处的、具有明确起始与终止条件的运行状态单元，它代表一个相对静止的控制阶段，是整个工艺流程被逻辑切分后的最小可控执行单位。</t>
+          <t>顺序控制设计</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>实际工作中常用三种实现方式：一是使用PLC内置的步进指令（如SFC块），结构清晰、调试直观，但对工程师逻辑建模能力要求高；二是用标志位+条件转移组合实现，灵活性强、兼容性好，但易因标志管理混乱导致流程跳步；三是借助HMI或上位系统下发步序号驱动PLC执行，适合多机协同场景，但增加通信依赖和故障排查难度。综合来看，在制造业单机设备控制中，采用标志位+条件转移的方式最常用——既满足产线现场快速修改、在线调试的需求，又避免了专用指令对PLC型号的强绑定，兼顾稳定性与维护效率。</t>
+          <t>步进流程设计</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1个异常情况概要：步未正常退出。具体情况：某装配工位完成夹紧动作后，因传感器信号抖动未被滤波，导致‘夹紧步’持续置位，后续步无法启动。解决思路：在步退出条件中嵌入防抖延时与双确认逻辑，且所有关键步退出必须由执行动作完成反馈+时间超限双重判据触发。1个复杂问题概要：多分支汇合处步序冲突。具体问题：两条并行装配线在合流工位需同步进入同一‘合装步’，但两路步序号到达时机不一致，造成PLC误判为流程错乱而停机。解决思路：在汇合点前设置统一的‘等待区步’，通过互锁标志+就绪信号握手机制协调进入，禁止直接合并步序号，确保合流动作严格按物理节拍对齐。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PLC控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>顺序控制设计</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>步进流程设计</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>请简单说说，当两个输出动作不能同时执行时，PLC程序中通常用什么逻辑关系来实现互锁？</t>
+          <t>PLC控制</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>通常用‘与非’逻辑关系来实现互锁，也就是在每个输出的启动条件中，加入另一个输出的常闭触点作为禁止条件。</t>
+          <t>顺序控制设计</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>实际工程中主要有三种互锁方式：一是硬接线互锁，通过接触器辅助触点物理串联，响应快、安全性高，但扩展性差、排查故障不便；二是PLC内部软互锁，在梯形图中用对方输出的反向状态做前置条件，灵活易修改，但依赖程序扫描周期和PLC运行状态；三是混合互锁，即软硬结合——软件做常规逻辑互锁，硬件做安全回路冗余保护，兼顾可靠性与可维护性。综合来看，混合互锁是当前制造业产线最主流的做法，既满足功能安全基本要求，又便于调试和后期变更。</t>
+          <t>动作条件互锁</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1个异常情况概要：互锁失效导致两个输出意外同时动作。具体情况：比如电机正反转接触器因PLC扫描延迟或程序跳转未覆盖所有分支路径，使正转和反转输出短暂重叠。解决思路：检查互锁逻辑是否覆盖所有启动/停止/急停/复位路径，强制在所有相关分支中嵌入对方输出的常闭条件，并在关键输出前增加脉冲边沿检测与延时确认。1个复杂问题概要：多工位协同场景下的级联互锁冲突。具体问题：一条装配线上多个气缸动作存在先后依赖和双向互斥，例如夹紧与顶升不能同启，但夹紧又需等待前序定位完成，此时单一互锁逻辑容易引发死锁或顺序紊乱。解决思路：将互锁从‘点对点’升级为‘状态机驱动’，用工序步序标志位统一管理各动作使能条件，互锁判断基于当前工艺步而非单纯输出状态，确保逻辑清晰、可追溯、易验证。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PLC控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>顺序控制设计</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>动作条件互锁</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>在PLC顺序控制中，当设备运行过程中突然发生气压不足报警，需要立即停止当前工序并退回到安全位置，此时应如何设计异常中断的响应逻辑？请简述关键步骤。</t>
+          <t>PLC控制</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>需在顺序控制流程中嵌入独立于主步序的、优先级更高的异常响应路径；该路径必须能实时捕获气压传感器信号触发的报警条件，并立即终止当前动作输出，同时激活预设的安全回退动作序列。</t>
+          <t>顺序控制设计</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>常见方案有三种：一是用PLC的中断指令直接跳转至专用异常处理段，响应最快但对硬件扫描周期依赖强；二是采用高优先级组织块或任务周期执行状态监控，兼顾实时性与逻辑可维护性；三是通过安全继电器硬线联锁切断动力后由PLC执行软逻辑复位，可靠性最高但回退动作稍慢。综合来看，第二种方案最常用——它既满足毫秒级响应要求，又便于在标准顺序功能图中统一管理报警源、动作约束和安全位置定义，符合产线调试与后期维保的实际需求。</t>
+          <t>异常中断处理</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1个异常情况概要：气压信号抖动导致误报。具体情况：气压传感器受振动或油污干扰，输出短暂低于阈值，引发非必要停机。解决思路：在PLC中设置带时间确认的滤波逻辑，要求报警信号持续保持一定时长才触发中断，同时保留原始信号用于故障追溯。1个复杂问题概要：退回途中二次故障。具体问题：设备正执行气动夹紧释放动作时触发气压报警，但退回路径需依赖另一组气缸，而该组也因同一气源问题无法动作。解决思路：将安全位置按层级预设，优先退回至最近的‘气路隔离点’而非最终原点，并在逻辑中固化各工序对应的安全停靠点及对应驱动条件，确保任何时刻都有可行退避路径。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>PLC控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>顺序控制设计</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>异常中断处理</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>在数控冲压设备的自动换模流程中，液压夹紧装置释放前，模具库转盘必须已精确定位并停止；而转盘一旦开始转动，夹紧装置必须维持夹紧状态。请简述这种双向依赖关系在PLC顺序控制中如何通过动作条件互锁实现，重点说明互锁条件中‘位置到位’与‘运动停止’两类信号应如何参与联锁判断。</t>
+          <t>PLC控制</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>这是典型的双条件互锁逻辑：夹紧装置释放动作，必须同时满足转盘‘位置到位’和‘运动停止’两个信号为真；而转盘启动动作，必须以夹紧装置处于‘夹紧状态’为前提。两类信号不可替代、不可合并，必须独立采集、独立验证，并在PLC程序中作为硬性前置条件参与每一步动作使能判断。</t>
+          <t>顺序控制设计</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>实际工程中常用三种实现方式：一是采用带确认延时的双沿触发逻辑，对位置传感器和速度反馈信号做去抖+延时确认，可靠性高但响应略滞后；二是用伺服驱动器内部的定位完成与零速保持信号直接接入PLC，时效性好但依赖驱动器接口一致性；三是结合安全PLC的双通道输入校验，兼顾功能安全与逻辑严谨，适合高风险换模场景。综合来看，第三种最稳妥——既满足ISO 13849-1的性能等级要求，又避免单点信号失效导致误动作。</t>
+          <t>动作条件互锁</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1个异常情况概要：位置传感器受油污或振动导致瞬时失信。具体情况：转盘已停稳，但位置信号短暂丢失，PLC误判未到位，阻断后续换模。解决思路：不依赖单一信号，将编码器零速维持时间、机械限位开关、位置传感器三者做‘二取二’表决，且设置合理确认窗口（如连续50ms稳定）。1个复杂问题概要：转盘惯性滑行导致‘运动停止’信号滞后于实际停稳。具体情况：伺服指令已撤，但转盘因负载惯量继续微转，速度信号未及时归零，造成夹紧释放延迟甚至超时报警。解决思路：在PLC中引入‘指令停止+编码器角位移变化率’复合判据，当指令停止后角位移变化量在设定阈值内持续100ms，即认定物理停止，不单纯等待速度信号归零。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PLC控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>顺序控制设计</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>动作条件互锁</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>在自动运行过程中，若检测到安全门被打开，系统需强制切换至手动模式且禁止自动重启。请简述PLC程序中如何通过输入信号与模式标志位配合实现这一安全联动。</t>
+          <t>PLC控制</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>在PLC程序中，需将安全门开关信号作为关键硬接线输入，接入具备安全响应能力的输入点；该信号在程序中不参与常规逻辑运算，而是直接作用于手自动模式标志位——一旦检测到门开信号有效，立即清零自动模式标志位、置位手动模式标志位，并锁存该状态，直至人工确认复位。</t>
+          <t>PLC程序结构</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>常见实现方式有四种：一是用单次扫描脉冲触发模式强制切换，响应快但易受干扰误动；二是采用带确认延时的边沿检测，可滤除抖动，但延迟约20毫秒；三是基于双通道安全输入+内部互锁标志位，兼顾可靠性和可诊断性；四是结合HMI操作权限校验后才允许复位。综合来看，第三种最常用——它既满足功能安全基本要求，又便于现场调试和故障追溯，且不依赖上位系统，符合产线自主可控原则。</t>
+          <t>手自动模式切换</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1个异常情况概要：安全门信号偶发瞬时抖动导致模式误切换。具体情况：机械振动或接线松动引发输入信号短暂通断，PLC误判为门开。解决思路：在输入处理层加入硬件滤波与软件去抖双重保护，且仅对上升沿（门开动作）启用锁存，下降沿不解除锁定。1个复杂问题概要：多工位共用同一安全回路时，局部门开触发全局停机与模式切换。具体问题：某工位门开，但其他工位仍在等待物料，强制全系统切手动会中断工艺节拍。解决思路：在模式标志位设计中引入区域级使能位，按安全分区独立管理手自动状态，主控逻辑只对受影响区域执行强制切换，其余区域保持待机但不退出自动模式。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PLC控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PLC程序结构</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>手自动模式切换</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>加减速曲线直接影响运动过程中的哪两个关键物理量？</t>
+          <t>PLC与运动控制</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>加减速曲线直接影响运动过程中的速度和位置这两个关键物理量。它决定了速度如何随时间变化，进而决定了位置随时间的累积变化。</t>
+          <t>运动控制</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>在自动化产线的实际调试中，常用加减速方案有梯形、S型和多项式三种。梯形曲线实现简单、PLC运算负担小，但启停冲击大，容易引起机械振动或定位偏差；S型曲线加加速度连续，运行平顺，对伺服系统和机械结构友好，适合高精度装配或高速分拣场景；多项式曲线灵活性更高，但需要更复杂的参数整定和PLC周期性计算，现场调试耗时长、容错性低。综合产线稳定性、调试效率和设备寿命，S型曲线是当前制造业自动化工程师最常选用的主流方案。</t>
+          <t>加减速曲线的作用</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1个异常情况概要：加减速过程中出现定位超调或抖动。具体情况：当S型曲线参数与伺服刚性不匹配，或机械负载突变时，实际位置响应滞后于规划轨迹，导致末端定位重复性下降。解决思路：优先在PLC侧微调S型曲线的加加速度限值，并同步观察伺服驱动器反馈的跟随误差趋势，再结合机械紧固状态和负载惯量实测进行闭环校准。1个复杂问题概要：多轴协同运动中单轴加减速特性不一致引发轨迹畸变。具体问题：例如在搬运机器人插补运动中，X轴用S型而Y轴仍用梯形，导致合成路径偏离预设轨迹。解决思路：统一各轴加减速类型与关键参数基准（如最大加加速度），通过PLC运动控制模块的轴组同步配置功能强制参数耦合，并在空载试运行阶段用激光跟踪仪验证合成轨迹精度。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PLC与运动控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>运动控制</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>加减速曲线的作用</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>请简述软件限位和硬件限位在功能上的主要区别。</t>
+          <t>PLC控制</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>软件限位是通过PLC程序中对轴的位置值进行实时判断，一旦超出设定范围就停止运动指令或触发报警；硬件限位是靠安装在机械本体上的物理开关或传感器，在运动部件实际触碰时直接切断驱动器使能或急停回路，强制终止运动。</t>
+          <t>运动控制调试</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>在产线调试中，常用三种组合方式：一是纯软件限位，响应快但依赖PLC扫描周期和程序可靠性，单点失效即失保；二是硬限位+软件限位双冗余，硬件作为最终兜底，软件用于预判减速和柔性保护，兼顾安全与效率；三是仅用安全继电器链路实现硬件限位，不经过PLC，符合电气安全等级要求，但无法实现位置预判和柔性处理。综合来看，双冗余方式最常用——既满足ISO 13849-1的性能等级要求，又支持调试阶段灵活调整限位位置，还便于后期维护时快速定位问题来源。</t>
+          <t>运动限位保护</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1个异常情况概要：设备运行中突然触发硬限位开关但无对应机械碰撞。具体情况：限位开关松动、积尘导致误触发，或振动引起瞬时通断。解决思路：先检查安装紧固性和防护状态，再用万用表测触点通断稳定性，必要时更换为带自清洁结构的工业级行程开关。1个复杂问题概要：软硬限位动作不一致导致频繁停机。具体问题：伺服电机存在惯性滑移，软件判断已超限但硬件尚未触发，或PLC与驱动器时间不同步造成逻辑错位。解决思路：在软件限位前增加预减速区段，并校准PLC位置反馈与驱动器编码器的实际同步关系，同时确认硬限位开关安装位置已考虑机械缓冲余量。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PLC控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>运动控制调试</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>运动限位保护</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>某包装机械的横封刀需要以恒定速度连续运行，同时允许上位系统随时调整其转速设定值，此时应采用哪种伺服控制模式？请简单说说该模式下速度指令是如何被接收和响应的。</t>
+          <t>PLC与运动控制</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>应采用速度控制模式。在这种模式下，伺服驱动器直接接收来自PLC或上位系统的模拟量电压信号或数字通信指令，作为目标转速给定值；驱动器内部闭环调节电机实际转速，使其持续跟踪该设定值。</t>
+          <t>伺服控制</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>实际工程中主要有三种实现方式：一是通过PLC的模拟量输出模块接4-20mA或0-10V信号给驱动器，响应快但抗干扰弱、精度受限；二是通过主流工业以太网协议（如EtherCAT或Profinet）下发数字速度指令，支持实时同步、多段变速和在线修改，是当前产线主流选择；三是用脉冲+方向信号，虽兼容老设备但动态响应慢、无法平滑调速。综合考虑稳定性、响应性和产线升级需求，推荐采用工业以太网数字通信方式，它既能满足横封工艺对速度平稳性的严苛要求，又便于后期与MES系统集成。</t>
+          <t>伺服控制模式区别</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1个异常情况概要：速度指令下发后电机无响应或跳变。具体情况：PLC通信正常、驱动器未报错，但实际转速始终为零或突增至最大值。解决思路：先确认驱动器是否已切换至速度控制模式并使能成功，再检查通信数据映射地址是否匹配、速度指令数值范围是否在驱动器允许区间内，最后核查PLC程序中指令更新周期是否过长导致指令未刷新。1个复杂问题概要：横封过程中频繁调速引发机械振动或封口不均。具体问题：上位系统按批次动态调整设定值，但加减速斜率未与机械惯性匹配，导致刀体抖动、封切力波动。解决思路：在PLC侧设置可配置的加减速时间参数，并与伺服驱动器的S曲线滤波功能协同启用；同时结合现场实测，将典型工况下的最优斜率固化为工艺参数模板，供不同产品规格调用。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PLC与运动控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>伺服控制</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>伺服控制模式区别</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>请简单说说伺服增益参数中‘积分增益’的主要作用是什么？</t>
+          <t>PLC与运动控制</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>积分增益主要用来消除伺服系统在稳态运行时的位置或速度误差，让实际运动结果更精确地跟踪设定目标。</t>
+          <t>伺服控制</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>在产线调试现场，工程师常用三种方式调整积分增益：一是手动试凑法，响应快但依赖经验，容易引发低频振荡；二是基于阶跃响应观察超调和回稳时间，判断积分作用强弱，兼顾时效与可复现性；三是借助PLC内置的自动整定功能（如支持模型辨识的伺服驱动器），能快速收敛参数，但需确保机械刚性达标且无明显负载突变。综合来看，优先采用自动整定+人工微调的组合方式——既保障调试效率，又避免因模型简化导致的过调风险。</t>
+          <t>伺服增益调整的影响</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1个异常情况概要：伺服电机低速爬行或停机后轻微晃动；具体情况：积分增益设置过高，导致系统持续累积微小误差并反复补偿，形成肉眼可见的蠕动或抖动；解决思路：先降低积分增益至零，确认是否消失；再逐步增加，同时监控指令与反馈的残差曲线，以残差稳定收敛且无周期性波动为边界。1个复杂问题概要：同一套伺服轴在不同负载工况下（如空载vs满载夹具）出现重复定位偏差；具体问题：积分增益无法兼顾全工况，轻载时响应过激，重载时补偿不足；解决思路：启用驱动器的负载自适应增益切换功能，或在PLC程序中根据实时电流/扭矩反馈动态缩放积分增益值，确保不同工况下稳态精度一致。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PLC与运动控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>伺服控制</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>伺服增益调整的影响</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>请简述编码器在伺服控制系统中反馈的主要物理量是什么？</t>
+          <t>PLC与运动控制</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>编码器在伺服控制系统中反馈的主要物理量是电机轴的实际旋转位置和转速。</t>
+          <t>伺服控制</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>在产线设备调试和维护中，工程师常通过三种方式获取这些反馈：一是增量式编码器，成本低、响应快，但断电后丢失位置，需每次上电回零；二是多圈绝对值编码器，断电不丢位置，适合需要精确定位的装配或贴标工位，但价格较高、接线稍复杂；三是带单圈绝对值的旋转变压器，抗干扰强、耐油污高温，常见于冲压、喷涂等恶劣工况设备，但需专用驱动器支持。综合来看，多圈绝对值编码器在当前主流伺服系统中应用最广，兼顾可靠性、精度与调试效率，是自动化工程师日常选型和故障排查的基准配置。</t>
+          <t>编码器反馈作用</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1个异常情况概要：编码器反馈值跳变或停滞。具体情况：设备运行中位置偏差突然增大，示波器或伺服驱动器监控界面显示反馈脉冲不连续或恒定不变。解决思路：先确认编码器电缆是否受机械拉扯或油污污染导致接触不良，再检查电机端与驱动器端接线端子是否松动，最后验证编码器本体是否因振动或过热出现内部光栅盘偏移。1个复杂问题概要：多轴协同时各轴反馈存在微小相位差。具体问题：在同步裁切或飞剪类应用中，即使指令一致，实际执行位置出现周期性累积误差。解决思路：不是单纯调高增益，而是进入驱动器参数层，启用编码器信号滤波补偿功能，并结合PLC运动控制模块的电子齿轮同步校准机制，对反馈延时做统一补偿。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PLC与运动控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>伺服控制</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>编码器反馈作用</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>在一条输送线的启停控制电路中，主电机和辅助破碎电机需要满足启动时主电机先运行、停机时辅助电机先停止的顺序要求，同时还要防止两者同时启动或同时停止。请简述如何通过电气互锁原理实现这一双向顺序保护，并说明关键元件的连接逻辑。</t>
+          <t>电气控制基础</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>电气互锁是通过接触器常闭触点串接在对方控制回路中，使两个回路不能同时得电。启动时，主电机接触器吸合后，其常闭触点断开，切断辅助电机启动回路，确保辅助电机无法先启动；停机时，辅助电机接触器释放后，其常闭触点复位闭合，才允许主电机接触器断电，从而保证主电机后停。</t>
+          <t>电气原理识读</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>常见实现方式有三种：一是纯继电器硬接线互锁，结构简单、响应快、故障易排查，但扩展性差、布线复杂；二是PLC软逻辑配合输出互锁，灵活性高、便于修改顺序逻辑，但依赖程序扫描周期和输出响应时间，存在微秒级延迟风险；三是继电器+PLC混合方案，用PLC控制主逻辑，关键顺序环节由硬件互锁兜底，兼顾可靠性与可维护性。综合制造现场对安全性和调试效率的要求，混合方案最常用，既满足IEC 61508 SIL1基础功能安全需求，又适配产线快速换型场景。</t>
+          <t>电气互锁原理</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1个异常情况概要：主电机接触器机械卡滞未释放，导致其常闭触点无法复位。具体情况是停机指令发出后，辅助电机已停，但主电机仍运转，且辅助电机无法再次启动。解决思路是增加接触器状态反馈信号接入PLC输入端，结合定时监测与超时报警，强制切断主回路并触发HMI提示。1个复杂问题概要：输送线多段联动时，该双电机顺序逻辑需嵌入更大启停链。具体问题是上游设备未就绪时，本段主电机误启动，破坏整体顺序。解决思路是在互锁基础上叠加‘允许启动’条件——将上游设备运行确认信号作为主电机启动回路的前置串联条件，用硬件常开触点实现，不依赖PLC扫描，确保本质安全。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>电气控制基础</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>电气原理识读</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>电气互锁原理</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>某装配工位的夹紧与送料机构由两个接触器分别控制，现场曾因误操作导致夹具未松开时送料气缸动作，造成工件挤压损坏。请简述如何利用电气互锁原理重构控制回路，从电路层面杜绝该类冲突动作，并解释互锁信号在启动和复位过程中的动态响应机制。</t>
+          <t>电气控制基础</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>在控制回路中，将夹紧接触器的常闭辅助触点串入送料接触器的线圈回路，同时将送料接触器的常闭辅助触点串入夹紧接触器的线圈回路，形成双向硬接线互锁。这样任一接触器得电时，另一接触器线圈回路被强制断开，物理上无法同时吸合。</t>
+          <t>电气原理识读</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>常见方案有三种：一是纯继电器硬互锁，响应快、无依赖、符合安全等级要求，但扩展性差；二是PLC软件互锁加输出点硬件串联，灵活性高且便于逻辑调整，但需确保输出模块故障不导致双动，必须配合安全继电器验证；三是安全继电器专用互锁模块，集成诊断与强制断开功能，适合高风险工位，但成本较高。综合可靠性、维护性和产线适配性，推荐采用安全继电器+关键输出点硬串联的混合方案，既满足电路级防冲突，又保留调试与诊断能力。</t>
+          <t>电气互锁原理</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1个异常情况概要：互锁触点粘连失效。具体情况：接触器辅助触点长期通断发热后熔焊，常闭触点无法断开，导致互锁失效。解决思路：选用带强制导向结构的辅助触点继电器，并定期点检触点状态，纳入设备预防性维护清单。1个复杂问题概要：手动调试模式下互锁被绕过。具体问题：维修或调机时为临时操作解除互锁，但未恢复或未同步更新HMI权限逻辑，导致复位后隐患残留。解决思路：将所有调试旁路开关接入安全继电器的使能输入端，且必须配合钥匙开关+操作日志记录，确保旁路动作可追溯、不可自动复位。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>电气控制基础</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>电气原理识读</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>电气互锁原理</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>某自动化产线新增一台PLC控制柜，设计时将PE保护导体从配电箱单独引至柜体接地端子，未与柜内N线端子连接。这种做法是否符合接地保护的基本原则？请简单说说理由。</t>
+          <t>电气控制基础</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>符合。接地保护的基本原则是确保故障电流有低阻抗回路快速触发保护动作，并保障人员接触设备外壳时无危险电压。PE线单独引至柜体接地端子、不与N线端子连接，正是为了保持保护导体路径独立、不混用，避免N线电位异常导致柜体带电。</t>
+          <t>电气原理识读</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>在自动化产线现场，常见三种处理方式：一是PE单独引接并做等电位联结，这是最稳妥的做法，抗干扰强、故障定位准；二是将PE与N在柜内一点共接，适用于老式TN-C-S系统改造，但易受N线不平衡电流影响柜体电位；三是通过接地排统一汇接多路PE，需严格控制接线顺序和压接质量，否则存在接触电阻超标风险。综合来看，第一种方式最适配当前主流产线——PLC控制系统对参考电位稳定性要求高，且便于后期扩展安全继电器、急停回路等独立保护链路。</t>
+          <t>接地与保护回路</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1个异常情况概要：柜门触电感明显。具体情况：PE线虽已引入，但柜体与门之间未加装编织接地跨接线，开门瞬间人体接触门板形成电位差回路。解决思路：检查所有可开启金属部件是否通过专用接地软线可靠连接至主接地端子，压接点须去漆、防松、导通测试合格。1个复杂问题概要：多台PLC柜共用同一接地干线时出现通信误码。具体问题：PE导体路径过长或分支过多，导致高频干扰沿接地路径耦合进信号地。解决思路：采用‘星型单点接地’结构，每台柜PE线独立敷设至总接地汇流排，避免链式串接；同时核查屏蔽电缆的屏蔽层仅在PLC侧单端接地，防止地环路引入噪声。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>电气控制基础</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>电气原理识读</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>接地与保护回路</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>当看到原理图上某根导线标注为“X1:05”，其中“X1”通常代表什么？</t>
+          <t>控制系统基础设计</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>X1代表第一块端子排的标识符，是电气原理图中对物理端子排的唯一编号，用于定位该导线在控制柜内实际接线位置。</t>
+          <t>电气原理图识读</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>在自动化工程现场，识别X1这类标识有三种常用方式：一是查图纸索引页，快速定位端子排布置图和对应设备；二是对照柜内实物标签，核对端子排本体印刷编号；三是调用设计交付包中的端子排清单表，按编号检索接线关系。第一种方式最快但依赖图纸完整性，第二种最直观但需停机操作，第三种最可靠且支持追溯，是当前主流项目交付标配，也是工程师日常调试和故障排查的首选路径。</t>
+          <t>端子排与线号对应</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1个异常情况概要：端子排实物编号与图纸标注不一致。具体情况：现场安装时端子排贴错标签，或图纸升版后未同步更新柜内标识。解决思路：先暂停接线变更，用万用表通断法反向验证X1:05的实际连接对象，再比对最新版图纸修订记录，确认是否属于已知升版项，最后协同设计方更新现场标识。1个复杂问题概要：多系统共用同一端子排导致X1编号含义模糊。具体问题：PLC、安全继电器、HMI信号共接入X1，但不同系统使用不同编号规则，造成X1:05在不同子系统图纸中指向不同功能点。解决思路：以主控系统（通常是PLC系统）的编号逻辑为基准，核查端子排侧的分段隔离标识和跳线配置，结合IO分配表逐点确认信号流向，必要时在端子排物理分段处加装隔板并重新标注功能区段。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>控制系统基础设计</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>电气原理图识读</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>端子排与线号对应</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>在一条多台变频器共用的PE接地干线中，若某台设备因绝缘破损导致外壳带电，而现场未设置等电位联结端子箱，此时仅依靠断路器跳闸来切断故障是否足够？请简述你的判断依据和关键风险点。</t>
+          <t>电气控制基础</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>不够。断路器跳闸依赖故障电流达到其脱扣阈值并维持足够时间，而PE干线共用且缺乏等电位联结时，故障电流路径阻抗高、分流分散，可能导致电流不足或响应滞后，无法可靠触发保护。</t>
+          <t>电气原理识读</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>常见应对方式有四种：一是加装独立PE支线直连柜体，降低回路阻抗，响应快但施工量大；二是增设局部等电位联结排就近连接设备外壳与PE干线，成本低、实施快，是当前产线改造首选；三是改用剩余电流动作保护器，对小电流漏电敏感，但易受变频器高频谐波干扰误动；四是升级为IT系统配绝缘监测，适合连续运行场景，但需配套改造且调试复杂。综合时效性、可靠性和产线适配性，优先采用局部等电位联结排方案。</t>
+          <t>接地与保护回路</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1个异常情况概要：变频器外壳带电但断路器不跳闸。具体情况：PE干线压接松动或锈蚀，导致故障电流被大幅削弱，低于断路器最小瞬动阈值。解决思路：逐段测量PE干线连续性与接触电阻，重点检查接线端子、汇流排连接点，用扭矩扳手按规范复紧并做防锈处理。1个复杂问题概要：多台变频器共地引发相互干扰型‘假接地’。具体问题：某台设备绝缘破损后，泄漏电流经共用PE窜入其他变频器控制端子，造成PLC误停机或模拟量漂移。解决思路：在每台变频器进线侧PE分支点加装隔离式等电位连接模块，物理隔离故障电流传播路径，同时核查控制信号线是否与PE同槽敷设，必要时分槽加屏蔽处理。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>电气控制基础</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>电气原理识读</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>接地与保护回路</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>某包装产线使用光电传感器检测透明塑料瓶的有无，但常因反光和环境光变化导致误判。请简单说说选型时应优先关注传感器的哪两类特性，并解释它们如何影响检测可靠性。</t>
+          <t>电气控制</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>第一类是抗环境光干扰能力，它决定了传感器在车间光照波动时能否稳定输出；第二类是针对透明物体的检测适应性，它直接影响对塑料瓶这类低反射率、易反光目标的识别准确率。</t>
+          <t>传感器应用</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>常见方案有四种：一是选用偏振滤光型光电开关，能有效抑制镜面反光，但对安装角度敏感；二是采用背景抑制型漫反射传感器，通过距离阈值区分瓶体与背景，调试便捷但需现场标定；三是用光纤式传感器配专用透镜，灵敏度高且抗干扰强，但成本高、布线复杂；四是组合双光路差分检测，稳定性最好但需要PLC逻辑配合。综合产线维护便利性和交付周期，背景抑制型是当前产线改造中最常用、最稳妥的选择。</t>
+          <t>传感器选型原则</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>异常情况概要：传感器频繁触发‘有瓶’假信号。具体情况：产线灯光调节后，环境光直射受光面，叠加瓶体曲面反射形成瞬时强光干扰。解决思路：现场加装遮光罩并调整传感器安装倾角，同时启用内置环境光补偿功能，不依赖额外硬件改造。复杂问题概要：同一批次透明瓶因材质批次差异导致部分瓶体几乎不可检。具体情况：新进原料添加了不同比例抗静电剂，改变了瓶体表面折射率和透光均匀性，使原有检测阈值失效。解决思路：在调试阶段预留多档灵敏度配置，通过扫码关联瓶型参数自动调用对应检测模式，由工程师在HMI上一键切换验证。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>电气控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>传感器应用</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>传感器选型原则</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>请简述NPN型和PNP型开关量传感器，它们的输出信号公共端分别接电源正极还是负极？</t>
+          <t>自动化设备基础</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NPN型传感器是漏型输出，工作时输出端相当于一个开关，连接到电源负极，因此它的公共端（即0V端）必须接电源负极；PNP型传感器是源型输出，输出端相当于一个开关，连接到电源正极，所以它的公共端（即24V端）必须接电源正极。两者都属于三线制开关量传感器，用于向PLC等控制器提供通断信号。</t>
+          <t>传感器应用</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>在自动化产线现场，工程师常需根据PLC输入模块类型匹配传感器：若PLC输入点为漏型输入，则优先选NPN传感器，接线简洁、抗干扰略优，但对现场共模电压敏感；若PLC为源型输入，则必须用PNP传感器，兼容性更广，尤其适合多品牌设备混用场景；也有部分新型PLC支持双模式输入，此时可统一选用PNP型，降低备件种类和调试复杂度；少数老旧产线存在NPN与PNP混用情况，需加装信号转换模块，但会增加故障点和响应延迟。综合来看，在当前主流国产及合资PLC系统中，PNP型因接线容错率高、与安全继电器/人机界面联动更直接，已成为制造业新建产线的首选方案。</t>
+          <t>传感器信号输出类型区别</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1个异常情况概要：传感器动作但PLC无信号响应。具体情况：现场常见于NPN传感器误接到源型输入PLC，或公共端未真正接入电源负极（如虚接、共地不良、开关电源负极未与PLC负极短接）。解决思路：先确认PLC输入类型标签，再用万用表测传感器输出端对PLC对应输入端的电压变化，重点检查公共端是否形成有效回路。1个复杂问题概要：同一电控柜内NPN与PNP传感器共存导致信号串扰或输入点损坏。具体问题：当两类传感器共用同一组电源且接地路径混乱时，可能引发参考电位漂移，造成部分输入点持续导通或烧毁光耦。解决思路：严格按类型分区供电，NPN组使用独立0V回路并单点接地，PNP组使用独立24V回路并单点接地，禁止在端子排上交叉混接公共端。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>自动化设备基础</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>传感器应用</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>传感器信号输出类型区别</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>一条装配线上使用接近开关检测金属零件位置，其输出为NPN型晶体管信号，而PLC输入端口配置为漏型接法。这种匹配关系下，传感器的信号是如何被PLC识别为有效状态的？请简述。</t>
+          <t>自动化设备基础</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>当NPN型接近开关检测到金属零件时，内部晶体管导通，将信号线拉低至接近0V，形成电流从PLC输入端口内部电源正极，经输入电路、传感器输出端，流向公共端（COM）构成回路；PLC检测到该低电平状态，即判定为有效信号。</t>
+          <t>传感器应用</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>实际工作中有三种常见接法：一是标准漏型匹配——NPN传感器直连漏型PLC输入，接线简洁、抗干扰好，是首选方案；二是误用源型接法——把NPN传感器接到源型PLC端口，会导致无法形成回路、信号始终无效；三是加装中间继电器或电平转换模块，虽能兼容但增加故障点和调试复杂度；四是改接PLC输入类型（如切换端子跳线或软件配置），但受限于硬件设计，多数紧凑型PLC不支持动态切换。综合可靠性、调试效率与维护成本，标准漏型匹配是最优解。</t>
+          <t>传感器信号输出类型区别</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1个异常情况概要：传感器有信号但PLC无响应。具体情况：现场接线正确，但PLC输入指示灯不亮，万用表测得传感器输出电压在动作时仅下降至2V左右，未达PLC低电平阈值。解决思路：检查传感器负载能力是否不足，确认PLC输入端口公共端（COM）是否与传感器电源负极共地，排查线缆压降或接触电阻过大问题。1个复杂问题概要：多台NPN传感器共用同一PLC漏型输入COM端时出现串扰。具体问题：某传感器动作时，相邻未动作通道也被误触发。解决思路：核查COM端布线是否过长或共享路径阻抗不均，优先采用分组独立COM接线；若硬件限制无法分组，则在每路信号线上加装隔离二极管或选用带反向截止特性的工业级NPN传感器。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>自动化设备基础</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>传感器应用</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>传感器信号输出类型区别</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>请简述急停回路必须采用常闭触点设计的原因。</t>
+          <t>电气控制设计</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>因为急停功能本质是‘故障导向安全’，常闭触点在正常运行时保持通路，一旦线路断开、触点熔焊失效、接线松脱或元件损坏，回路自动断开，强制设备停止，确保人员和设备安全。</t>
+          <t>安全回路设计</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>目前主流有三种实现方式：一是纯硬接线常闭串联回路，可靠性最高、响应最快，但扩展性差、排查耗时；二是带安全继电器的常闭回路，兼顾诊断能力和抗干扰性，支持回路监控，是当前产线改造和新项目最常用方案；三是基于安全PLC的分布式常闭输入，适合大型系统，但对布线规范和接地要求极高，调试周期长。综合来看，在制造业自动化工程师日常工作中，安全继电器方案平衡了安全性、可维护性和实施效率，是产线设计与运维中最务实的选择。</t>
+          <t>急停回路设计原则</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1个异常情况概要：急停按钮按下后设备未停止。具体情况：常闭触点因长期使用发生机械卡滞或触点氧化，导致按下后未能可靠断开。解决思路：定期执行触点阻值测试和手动操作验证，将急停按钮纳入预防性维护清单，每次停机检修时必检。1个复杂问题概要：多台设备共用急停回路时出现误触发。具体问题：不同设备急停信号串接过长，分布电容和线路干扰引发瞬时断路假信号。解决思路：按区域划分独立安全回路，采用双通道+时间监测的安全继电器进行信号滤波，并在主控侧增加最小断开时间阈值校验。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>电气控制设计</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>安全回路设计</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>急停回路设计原则</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>请简单说明急停回路中‘双通道’设计主要防范哪类故障。</t>
+          <t>电气控制设计</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>双通道设计主要防范单一元件失效导致急停功能丧失的故障，比如一个触点粘连、一根导线断开或一个继电器线圈失电等单点硬件故障。</t>
+          <t>安全回路设计</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>在制造业产线现场，常见的双通道实现方式有三种：一是采用两个独立物理回路加双冗余安全继电器，可靠性高但布线和调试成本较高；二是用带诊断功能的安全PLC模块直接采集双触点信号，集成度高、诊断及时，但对工程师选型和配置能力要求更高；三是使用机械式双断点急停按钮配合单安全继电器，成本低但无法识别通道间时序偏差。综合来看，第二种方案在当前主流产线中应用最广——它能在保证响应时间不超安全要求的前提下，兼顾诊断覆盖性、维护便利性和系统可扩展性。</t>
+          <t>急停回路设计原则</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1个异常情况概要：急停按钮按下后设备未停止。具体情况：双通道信号到达时间差超过安全模块允许阈值，被判定为‘非同步动作’而拒绝执行停机。解决思路：现场排查按钮内部弹簧疲劳或接线端子压接松动导致两路触点动作不同步，优先更换按钮并复测动作一致性。1个复杂问题概要：产线改造中新增设备接入原有双通道急停回路后频繁误触发。具体问题：新设备急停触点响应延迟略长，与原回路时序匹配失效。解决思路：不简单缩短安全模块响应窗口，而是通过分段验证法定位延迟源，在接口侧加装带延时补偿功能的安全耦合器，确保整条链路满足‘故障导向安全’原则。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>电气控制设计</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>安全回路设计</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>急停回路设计原则</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>请简述急停按钮触发后，安全回路应满足的最基础动作要求。</t>
+          <t>电气控制设计</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>急停按钮触发后，安全回路必须立即切断所有驱动类执行器的动力电源，包括电机主回路和伺服使能信号；同时，不得依赖软件延时、PLC扫描周期或上位机指令来执行该动作——切断动作必须由硬件安全元件直接完成。</t>
+          <t>安全回路设计</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>目前主流有三类实现方式：一是采用双通道安全继电器，响应快、验证成熟，但扩展性弱、接线复杂；二是使用集成安全功能的PLC模块，配置灵活、便于诊断，但需确保其安全等级覆盖整条回路且未被普通逻辑误覆盖；三是采用分布式安全控制器配合安全I/O，适合大型产线，但对现场布线和参数同步要求高。综合来看，在制造业自动化产线中，双通道安全继电器仍是当前最稳妥、验收通过率最高的方案，因其动作路径最短、失效模式最透明，且与各类老旧设备兼容性最好。</t>
+          <t>急停回路设计原则</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1个异常情况概要：急停触发后部分电机停止，但某台伺服仍微动。具体情况：安全回路已断开使能信号，但伺服驱动器内部电容残余能量未及时泄放，或抱闸延迟释放。解决思路：核查伺服驱动器安全输入端子是否直连安全回路、抱闸供电是否受同一安全链控制，并在驱动器侧增加安全停机模式（如SS1）配合机械制动验证。1个复杂问题概要：多工位协同设备中，一个急停点触发后，其他工位无法复位。具体问题：安全回路采用串联式‘蘑菇头’级联，但某处接线松动或触点氧化导致回路通断状态不可靠，复位信号无法闭环确认。解决思路：改用带回读反馈的安全继电器，或在关键节点增设安全回路状态监测点，结合物理验电与逻辑自检双重确认复位条件。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>电气控制设计</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>安全回路设计</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>急停回路设计原则</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>在机械设备的急停回路设计中，为什么必须采用硬接线方式实现急停信号的切断，而不是依赖PLC程序逻辑来执行？请简述主要原因。</t>
+          <t>电气控制设计</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>因为急停功能属于最高优先级的安全保护动作，必须在任何控制层失效时仍能可靠触发；硬接线绕过PLC扫描周期、程序中断、通信延迟和软件故障等所有可编程环节，确保从按下按钮到切断动力源的响应不受控制器状态影响。</t>
+          <t>安全回路设计</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>目前主流方案有三种：一是纯继电器硬接线回路，响应快、结构简单，但扩展性差、诊断能力弱；二是安全继电器模块+硬接线，兼顾响应速度与状态反馈，支持回路自检，是当前产线最常用方案；三是带安全认证的可编程安全控制器，虽保留部分逻辑灵活性，但仍要求关键断电路径全程硬接线直连。三者都强制要求急停信号不经过普通PLC的输入扫描和程序处理环节。综合来看，安全继电器方案在可靠性、可维护性和成本之间平衡最优，已成为制造业自动化工程师实施急停回路的默认选择。</t>
+          <t>急停回路设计原则</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1个异常情况概要：急停按钮按下后设备未停止。具体情况：常闭触点因油污或机械卡滞未能断开，或接线端子松动导致回路虚接。解决思路：必须在调试阶段执行‘回路导通性+强制断开’双验证，使用专用安全测试仪逐段测量触点动作状态和回路电阻，并在设备运行前做三次以上带载急停实测。1个复杂问题概要：多台设备共用急停链路时出现误动作或拒动。具体问题：不同设备急停回路接地电位不一致或电缆分布电容引发感应电压，导致安全继电器误判回路断开。解决思路：统一采用双通道+监控触点的安全继电器，所有急停器件共用同一参考地，长距离布线加装屏蔽双绞线并单端接地，链路末端增加终端电阻匹配。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>电气控制设计</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>安全回路设计</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>急停回路设计原则</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>急停回路中常使用带强制导向触点的继电器，这种设计主要解决什么安全问题？请简述其作用原理。</t>
+          <t>电气控制设计</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>它主要解决触点熔焊后仍能可靠断开的安全失效问题。当急停按钮被按下时，必须确保控制回路物理切断，即使某个触点因过载或电弧发生粘连，也不能影响整体断开功能。</t>
+          <t>安全回路设计</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>目前产线主流有三种实现方式：一是单只强制导向继电器配双通道输入，结构简洁但单点故障率略高；二是双继电器冗余配置，两套触点机械联动，抗熔焊能力最强，是当前新项目首选；三是用安全PLC模块替代，响应快但成本高、调试周期长，多用于柔性产线升级场景。综合来看，双继电器强制导向方案在可靠性、成本和交付效率上最均衡，是制造业自动化工程师在新建或改造产线时最常采用的方案。</t>
+          <t>急停回路设计原则</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1个异常情况概要：急停复位后设备意外重启。具体情况：两个强制导向触点中一个已熔焊，另一个虽断开但未触发安全回路自检失败，导致复位信号误通过。解决思路：必须在复位回路中加入‘断开验证’逻辑——即复位前先检测两通道是否均为断开状态，任一通道未断开则禁止复位。1个复杂问题概要：多台设备共用急停总线时的级联失效。具体问题：某台设备的强制导向继电器触点卡死在闭合位，导致整条急停链无法真正切断。解决思路：采用分段式急停架构，每3～5台设备设独立安全继电器作为区域节点，并配置通道级状态反馈至主控系统，实现故障定位与局部隔离。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>电气控制设计</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>安全回路设计</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>急停回路设计原则</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>安全门联锁逻辑中，‘门未关到位时设备不能启动’这一要求依据的是哪一条基本安全原则？</t>
+          <t>电气控制基础</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>这条要求依据的是‘失效导向安全’原则，也就是当安全相关部件出现故障或异常状态时，系统必须自动进入安全状态，而不是继续运行或进入危险状态。</t>
+          <t>安全控制基础</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>在实际产线部署中，主要有四种实现方式：一是用机械式限位开关配合硬接线回路直接切断主控电源，响应快但维护频次高；二是用带诊断功能的安全继电器接收双通道信号，抗干扰强、符合主流认证要求；三是用安全PLC通过双通道输入和内部表决逻辑判断门状态，灵活性高但调试周期稍长；四是集成式安全控制器配合IO-link安全模块，布线简洁且支持状态追溯，但对现场工程师的配置能力要求更高。综合来看，安全继电器方案在中小产线中落地最稳、验证最充分，是当前制造业自动化工程师最常选用的平衡方案。</t>
+          <t>安全门联锁逻辑</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1个异常情况概要：安全门频繁误报未关到位。具体情况：门体轻微变形或限位开关松动导致触点接触不稳定，系统反复判定为‘未关到位’而阻断启动。解决思路：先做物理紧固和间隙复测，再用万用表实测触点通断一致性，必要时更换带自诊断功能的冗余型开关。1个复杂问题概要：多扇安全门协同联锁逻辑冲突。具体问题：某装配工位含三道互锁门，其中一扇门维修后重新标定，但未同步更新其他门的状态依赖关系，导致整条线无法复位。解决思路：以安全回路图为基础，逐点核验各门信号在安全控制器中的输入映射与逻辑组态，重点确认‘所有门必须同时满足’还是‘任一未关即停’这类基础逻辑配置是否统一。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>电气控制基础</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>安全控制基础</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>安全门联锁逻辑</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>在安全门联锁逻辑里，为什么必须使用安全等级的输入信号来检测门状态？</t>
+          <t>电气控制基础</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>因为普通输入信号不具备故障检测和冗余表决能力，无法确保在接线松动、触点粘连、短路或断线等常见失效情况下仍能及时、可靠地触发停机；而安全等级输入信号通过双通道采集、实时自检和故障诊断机制，从源头保障门状态判断结果的真实性和可信度。</t>
+          <t>安全控制基础</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>目前主流有三类实现方式：一是采用带诊断功能的安全继电器模块接收双触点门开关信号，优势是结构简单、验证成熟，但扩展性差、调试周期长；二是用安全PLC直接读取符合安全等级的双通道输入模块信号，灵活性高、支持复杂逻辑，但对工程师安全编程能力要求高；三是集成式安全控制器配合IO-Link安全传感器，部署快、诊断信息丰富，但对现场布线和设备兼容性有更高要求。综合产线维护效率、验证成本和长期可靠性，安全PLC方案在新建及改造项目中已成为首选。</t>
+          <t>安全门联锁逻辑</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1个异常情况概要：门开关触点单边失效未被识别。具体情况：一侧常闭触点因油污导致接触电阻升高，在安全控制器中未达断开阈值，系统误判为门已关闭。解决思路：启用输入通道的实时阻抗监测功能，结合周期性回读校验，将‘信号稳定’与‘物理通断’双重确认纳入安全响应条件。1个复杂问题概要：多扇安全门存在互锁优先级冲突。具体问题：某工位含主门、观察窗门和维修盖板三处安全接入点，当维修盖板打开时本应允许主门手动操作，但现有逻辑造成全区域急停。解决思路：在安全程序中构建带使能链的分层门状态模型，以物理操作权限为依据动态更新各门的‘可忽略’状态标识，并通过安全总线同步各节点的门状态上下文，确保联锁动作既不漏报也不误动作。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>电气控制基础</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>安全控制基础</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>安全门联锁逻辑</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>请简单说说安全继电器与普通继电器在触点设计上的关键区别。</t>
+          <t>电气控制基础</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>安全继电器的触点设计采用强制导向结构，确保常开和常闭触点机械联动、物理互锁；而普通继电器的触点是独立动作的，没有强制关联机制。</t>
+          <t>安全控制基础</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>在自动化产线的安全回路搭建中，工程师常用三种触点配置方案：一是单通道配强制导向触点，响应快但需配合外部监控回路；二是双通道冗余配强制导向触点，能自动检测触点熔焊或粘连，可靠性高；三是多组触点串联加自检逻辑，适合高风险区域如冲压机急停回路。其中双通道冗余配强制导向触点是当前制造业主流选择，它兼顾诊断能力、响应时效和现场维护便利性，避免因单点失效导致安全功能丧失。</t>
+          <t>安全继电器应用</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1个异常情况概要：安全继电器输出触点出现熔焊粘连。具体情况：某装配工位急停按钮按下后设备未停机，排查发现安全继电器常闭触点因长期大电流反复动作发生熔焊，导致安全回路无法断开。解决思路：立即停线更换同型号安全继电器，并核查该回路实际负载电流是否超出触点额定值，同步检查急停按钮触发频次是否异常升高，必要时优化工艺节拍或加装缓冲电路。1个复杂问题概要：安全继电器与PLC安全模块混用导致触点状态冲突。具体问题：产线改造中将原有安全继电器输出接入新PLC的安全输入端子，但未切断原继电器自检反馈回路，造成两个安全器件相互误判为故障。解决思路：严格按安全回路层级划分原则，明确主控责任单元，拆除交叉反馈线，统一由安全继电器执行最终输出控制，PLC仅作状态监视不参与安全逻辑判定。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>电气控制基础</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>安全控制基础</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>安全继电器应用</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>在设备运行过程中，安全门被意外打开时，控制系统需要立即停止危险动作。请简述安全门联锁逻辑中，如何通过硬件信号实现这一紧急停机功能。</t>
+          <t>电气控制基础</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>安全门联锁逻辑的硬件实现，核心是将安全门的开闭状态转化为可靠的电气信号，直接接入控制器的安全输入端口；该信号必须在门打开瞬间断开回路，触发控制器立即切断动力输出，且整个过程不经过普通程序扫描周期，由硬件电路独立完成响应。</t>
+          <t>安全控制基础</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>目前主流有三种实现方式：一是使用双通道安全继电器，两路常闭触点串联接入急停回路，抗单点故障能力强，响应快、无需编程，但扩展性弱；二是采用带安全认证的PLC安全输入模块，支持诊断和状态监控，便于集成到整机安全系统，但成本高、需专业配置；三是用安全光幕或安全门锁开关直连安全控制器，信号经冗余回路校验后驱动安全输出模块切断伺服使能和主电源接触器。综合来看，第二种方案在产线升级和多工位协同场景下最常用——它兼顾响应时效（毫秒级）、可追溯性与后期维护便利性，是当前新装及技改项目的首选。</t>
+          <t>安全门联锁逻辑</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1个异常情况概要：安全门开关触点粘连。具体情况：机械磨损或油污导致常闭触点无法物理分离，门已打开但信号仍保持导通，系统误判为安全状态。解决思路：定期执行手动脱扣测试，结合安全模块的周期性自检功能，在每次开机或换班时强制验证触点动作有效性。1个复杂问题概要：多扇安全门共用同一安全回路时的故障定位难。具体问题：某扇门故障导致整条产线停机，但无法快速判断是哪一扇门或哪一段线路异常。解决思路：在每扇门分支回路中加装带地址识别的安全接线盒，配合安全控制器的分段诊断功能，实现故障点自动上报至HMI，缩短平均修复时间。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>电气控制基础</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>安全控制基础</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>安全门联锁逻辑</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>当设备的安全门被打开时，安全继电器如何确保电机立即断电且无法意外重启？请简单说说它依赖的关键机制。</t>
+          <t>电气控制基础</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>安全继电器通过双通道输入监测安全门开关状态，一旦任一通道信号中断（如门打开），内部强制导向触点立即切断电机主回路供电；同时利用反馈回路验证输出触点实际断开状态，并在复位前强制要求所有安全条件重新满足，防止带故障重启。</t>
+          <t>安全控制基础</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>实际工程中常用三种实现方式：一是纯硬件安全继电器方案，响应快、无需编程、抗干扰强，但扩展性差、功能固定；二是安全PLC加安全模块方案，灵活性高、可集成诊断，但配置复杂、对工程师安全编程能力要求高；三是带安全功能的智能驱动器直控方案，节省接线、响应极快，但仅适用于驱动器直驱场景，不兼容传统接触器控制。综合产线可靠性、调试效率和维护便利性，制造业现场仍以硬件安全继电器为主流选择，尤其在冲压、装配等高风险工位。</t>
+          <t>安全继电器应用</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1个异常情况概要：安全门开关触点粘连未断开。具体情况：机械磨损或油污导致常闭触点失效，门已打开但信号仍为‘闭合’，安全继电器无法触发断电。解决思路：采用双断点开关+定期功能测试，结合安全继电器自检周期内强制执行输出触点断开验证。1个复杂问题概要：多安全门串联后单点故障导致整机停机。具体问题：产线含5个安全门串联接入同一安全继电器，任一门故障即全线停产，影响OEE。解决思路：改用带区域监控功能的安全继电器，分组接入并独立诊断各门状态，通过安全总线将故障定位信息实时传至HMI，既保障安全又缩小停机范围。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>电气控制基础</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>安全控制基础</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>安全继电器应用</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>请简述故障安全原则的核心要求是什么？</t>
+          <t>电气控制</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>故障安全原则的核心要求是：当控制系统或其相关部件发生任何单一故障时，整个安全回路必须自动导向安全状态，且该导向过程不依赖人为干预、不依赖外部监控系统、也不依赖故障后的人为复位动作。</t>
+          <t>安全回路集成</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>在制造业自动化现场，工程师常采用三种集成方式：一是基于双通道冗余输入+安全继电器的硬接线方案，响应快、验证成熟，但扩展性差、诊断能力弱；二是使用带安全功能的PLC配合安全I/O模块，灵活性高、支持诊断和远程复位，但对编程规范和安全配置经验要求高；三是采用集成安全逻辑的智能驱动器直接接入安全总线，节省布线、响应更快，但对设备选型和厂商生态依赖强。综合时效性、可维护性和产线适配性，第二类——安全PLC加安全I/O的方案在当前新建及改造产线中应用最广、平衡性最好。</t>
+          <t>故障安全原则</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1个异常情况概要：安全输入信号偶发丢失但无硬件报警。具体情况：光电保护装置信号在运行中短暂中断，安全PLC未触发停机，但安全状态监视灯未熄灭。解决思路：优先检查接线端子压接可靠性与电磁干扰源，再验证安全输入模块的滤波时间设置是否过长，最后确认安全程序中是否误用了非安全指令屏蔽了故障响应。1个复杂问题概要：多台设备共用同一安全急停回路时，单点故障导致全线误停。具体问题：某输送段急停按钮触点粘连，使整条装配线所有工位同步停机。解决思路：按工艺节拍和风险隔离原则重构安全分区，将物理上独立的设备组划分为不同安全回路，采用带区域识别功能的安全主站实现选择性停机，并同步更新安全评估文档和操作规程。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>电气控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>安全回路集成</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>故障安全原则</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>请简单说说‘失电导向安全’这一设计方式的基本含义。</t>
+          <t>电气控制</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>失电导向安全，是指在电气控制系统中，当电源中断、控制信号丢失或关键元件失效时，系统能自动进入预设的安全状态，比如停止运动、释放夹具、切断动力输出。它的核心是依靠物理设计实现‘无电即安全’，而不是依赖软件逻辑或持续供电来维持安全。</t>
+          <t>安全回路集成</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>在制造业产线的自动化设备上，常用三种实现方式：一是采用带弹簧复位的失电制动器，断电即抱闸，响应快但需定期检查机械磨损；二是使用双通道安全继电器构成的硬接线安全回路，抗干扰强、认证成熟，但扩展性差、故障定位慢；三是基于安全PLC的模块化方案，支持诊断和灵活配置，但对工程师的集成能力要求高。综合来看，在新建产线或技改项目中，安全PLC方案更优——它兼顾实时性、可维护性和合规性，且能与主流伺服驱动器的急停链路无缝对接，满足当前产线柔性换型的实际需求。</t>
+          <t>故障安全原则</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1个异常情况概要：安全继电器输出触点粘连。具体情况：某包装机急停后电机仍微转，经查是安全继电器常闭触点因长期大电流拉弧而熔焊粘连，导致失电后安全回路未能真正断开。解决思路：在选型阶段明确触点负载等级与实际切断电流匹配，投产前做触点寿命验证，并在日常点检中加入触点阻值测量项。1个复杂问题概要：多轴协同设备中部分轴失电而其他轴未同步进入安全状态。具体问题：一台四轴码垛机器人中，末端执行器断电抱闸，但底座旋转轴因安全信号传递延迟仍在惯性转动，造成碰撞风险。解决思路：必须将所有动力轴的安全使能信号统一由同一安全回路触发，并通过硬件级联而非软件转发确保动作同步；同时在机械布局阶段预留安全响应时间裕量，校核各轴最大滑行距离是否在防护边界内。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>电气控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>安全回路集成</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>故障安全原则</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>在一条装配线的急停回路中，安全继电器需要同时监控双手按钮和光幕两个输入信号。当光幕被遮挡时设备必须立即停止，但双手按钮需满足‘同时按下且持续保持’才允许启动。请简述如何用安全继电器实现这一双重安全逻辑，并说明关键接线与验证要点。</t>
+          <t>电气控制基础</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>安全继电器需配置两组独立安全通道：一组接入光幕的常闭安全输出，实现遮挡即断开、强制停机；另一组接入双手按钮的双通道信号，要求两个按钮触点分别接入不同通道，且仅当两者同步闭合并持续保持时，安全继电器才输出启动使能。所有安全输入必须使用符合标准的正逻辑接线，输出驱动主接触器线圈回路。</t>
+          <t>安全控制基础</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>常见实现方式有三种：一是选用带双手控制功能模块的单台安全继电器，集成时序与同步判断，接线简洁但扩展性弱；二是用双通道安全继电器加外部时间监测模块，灵活性高但增加故障点；三是采用可配置安全控制器，支持逻辑编程，适合多工位联动但对工程师配置能力要求高。综合可靠性、调试效率与产线维护便利性，首选第一种——集成式双手控制型安全继电器，它已内建防单点失效、响应时间校验和通道交叉检测，最适配产线现场快速部署与一线人员理解。</t>
+          <t>安全继电器应用</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1个异常情况概要：光幕误触发导致频繁停机。具体情况：现场存在反光、粉尘或人员衣袖偶然进入检测区，引发非危险性遮挡。解决思路：现场实测光幕安装高度与盲区，调整灵敏度档位，加装物理遮罩隔离干扰源，并在安全继电器中启用可调延时消抖（非屏蔽型），确保遮挡持续超过40毫秒才触发停机。1个复杂问题概要：双手按钮其中一个触点粘连未释放。具体问题：操作员松开一个按钮后，该通道仍保持导通，导致安全继电器误判为‘持续同步按下’，形成启动条件假象。解决思路：依赖安全继电器的通道间定时比较功能，在每次启动循环中强制检测两通道闭合/断开时刻差；若偏差超15毫秒，立即锁定输出并触发故障指示，同时要求按钮必须采用强制断开结构，并在季度点检中用专用测试仪验证触点机械复位性能。</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>电气控制基础</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>安全控制基础</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>安全继电器应用</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>请简单说说Modbus TCP协议通常运行在哪一层网络模型上。</t>
+          <t>PLC与运动控制</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Modbus TCP协议运行在TCP/IP网络模型的传输层和应用层之间，具体来说，它是在传输层的TCP协议之上构建的应用层通信协议。</t>
+          <t>工业通信</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>在自动化工程师日常工作中，实现PLC与HMI、SCADA或伺服驱动器之间的数据交互时，常用三种通信承载方式：一是纯Modbus TCP直连，优势是配置简单、兼容性广，但缺乏设备状态监控和故障自恢复能力；二是通过工业以太网网关桥接Modbus RTU转TCP，适合老旧设备利旧，但增加单点故障风险且存在转换延迟；三是采用支持Modbus TCP的嵌入式控制器直接集成，实时性好、拓扑清晰，但对设备选型和固件版本有要求。综合来看，在新建产线或设备升级场景中，优先选用原生支持Modbus TCP的PLC与智能驱动器直连，兼顾部署效率、诊断能力和后期维护便利性。</t>
+          <t>常见工业总线类型</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1个异常情况概要：Modbus TCP连接频繁断开。具体情况：现场出现周期性通信中断，但网络物理指示灯常亮，Ping测试通但读寄存器超时。解决思路：先排查交换机端口是否启用了节能模式或风暴抑制，再确认PLC与从站之间是否存在未收敛的ARP缓存或IP地址冲突，最后检查双方TCP保活时间设置是否匹配。1个复杂问题概要：多主站同时访问同一Modbus TCP从站导致数据错乱。具体问题：两台HMI分别轮询同一伺服驱动器，偶尔出现位置值跳变或写指令丢失。解决思路：必须由主控PLC统一分配访问时序，禁用非主控设备的主动轮询，改用事件触发+缓存同步机制，并在驱动器侧启用写保护和事务校验功能。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>PLC与运动控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>工业通信</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>常见工业总线类型</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>当一台带安全光幕的冲压设备运行时，光幕被遮挡后设备应立即停止。这个‘立即停止’的要求，是如何通过故障安全原则在硬件回路上体现的？请简单说说。</t>
+          <t>电气控制</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>故障安全原则在硬件回路上的体现，是让安全功能在发生断线、短路、元件失效等常见故障时，自动导向安全状态——也就是设备停机。具体到光幕回路，就是把光幕的输出信号接入安全继电器或安全控制器的专用输入端，再通过冗余触点、强制导向结构和自检机制，确保任一单点故障都不会导致停机功能失效。</t>
+          <t>安全回路集成</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>目前主流有三种实现方式：一是采用双通道+交叉监测的安全继电器，结构简单、响应快，但扩展性差，适合单光幕单执行器场景；二是用安全可编程控制器加专用安全输入模块，灵活性高、支持多条件联锁，但调试门槛略高；三是集成式安全驱动器直连光幕与制动回路，省去中间继电器，响应最快，但对设备兼容性要求严。综合可靠性、调试效率和产线维护习惯，双通道安全继电器仍是冲压类设备最常用、最稳妥的选择。</t>
+          <t>故障安全原则</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1个异常情况概要：光幕供电回路虚接导致间歇性失电。具体情况是设备运行中光幕偶尔‘假复位’，安全继电器未报错但实际失去防护。解决思路是检查电源端子压接质量，改用弹簧端子替代螺丝端子，并在安全回路中增加电源状态监控反馈至主控。1个复杂问题概要：光幕与滑块制动执行器之间存在机械惯性延迟。具体问题是即使安全回路已断开，滑块仍可能越过下死点造成伤害。解决思路是将安全光幕信号与滑块位置信号做时间-距离预判联动，在光幕触发瞬间提前启动制动，并通过实际停机验证曲线校准动作窗口。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>电气控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>安全回路集成</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>故障安全原则</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>在一条产线设备中，PLC需要实时读取伺服驱动器的位置反馈数据，同时向其发送速度指令，你会选择哪种工业总线来实现这种双向高速数据交互？请简述选择理由。</t>
+          <t>PLC与运动控制</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>我会优先选择支持实时运动控制的专用工业以太网总线，比如EtherCAT或Powerlink这类具备纳秒级同步精度、周期性数据交换能力的方案。</t>
+          <t>工业通信</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>实际产线选型中，常见方案有四种：一是传统Modbus RTU，成本低但刷新慢、无硬件同步，难以满足高动态响应需求；二是CANopen，实时性优于Modbus，但带宽和节点扩展性受限，多轴协同时易出现延迟累积；三是EtherNet/IP，兼容性好、生态成熟，但标准模式下依赖软件调度，确定性需额外配置；四是EtherCAT，采用分布式时钟机制，一个周期内完成所有从站读写，位置反馈与速度指令可严格同步，且布线灵活、调试工具链完善。综合产线对响应一致性、多轴同步精度和现场维护便利性的要求，EtherCAT是最稳妥的选择。</t>
+          <t>常见工业总线类型</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1个异常情况概要：伺服位置反馈跳变或丢失。具体情况：现场电磁干扰导致总线帧校验失败，PLC连续收到无效位置值。解决思路：核查屏蔽层单端接地是否规范，检查终端电阻是否启用，临时启用总线诊断功能定位故障节点，再结合示波器观察信号眼图质量。1个复杂问题概要：多台伺服共用同一总线时，某轴指令滞后半拍。具体问题：拓扑结构为长链式布线且未做阻抗匹配，信号反射引发时序偏移。解决思路：改用菊花链末端回环接法，缩短分支长度，配合PLC内置的同步偏差补偿参数微调各轴时间戳基准。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>PLC与运动控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>工业通信</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>常见工业总线类型</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>某产线安全门开关采用常闭触点接入安全回路，但现场发现有人用胶带将开关强行压合保持导通。从故障安全原则出发，这种做法违背了哪一核心要求？请说明理由。</t>
+          <t>电气控制</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>违背了‘失效导向安全’这一核心要求。故障安全原则要求：当安全相关部件发生任何单一故障（包括人为误操作、机械卡滞、接线松动等）时，系统必须自动进入预设的安全状态。用胶带强制压合常闭触点，使开关失去检测门开闭的能力，一旦门实际打开，回路仍被错误维持导通，无法触发停机，丧失了故障时应有的保护功能。</t>
+          <t>安全回路集成</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>常见应对方案有四种：一是使用双通道冗余安全开关，配合安全继电器或安全PLC进行交叉监测，抗单点误动作能力强，但成本较高；二是采用带强制断开结构的机电式安全门锁，物理上防止胶带类违规压合，部署简单、可靠性高，是当前产线改造首选；三是加装独立的门位置传感器与安全控制器做逻辑比对，可识别异常状态，但需额外布线和调试；四是通过HMI弹窗+权限管控限制人员绕过操作，属管理辅助手段，无法替代硬件级防护。综合来看，强制断开式安全门锁方案在时效性、可靠性与落地成本上最平衡，一线工程师最常优先选用。</t>
+          <t>故障安全原则</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>1个异常情况概要：安全门开关触点氧化导致接触电阻增大。具体情况：常闭触点表面微氧化后，在安全回路中形成高阻通路，安全继电器可能无法可靠识别断开，造成‘假导通’。解决思路：定期执行触点通断测试并记录阻值趋势，结合设备运行小时数制定预防性更换周期，不依赖目视检查。1个复杂问题概要：多扇安全门共用同一安全回路时出现误停机。具体问题：其中一扇门开关响应延迟或抖动，导致回路短暂中断，引发整条产线非计划停机。解决思路：为每扇门配置独立安全输入通道，采用带时间滤波与状态确认机制的安全控制器，同时设置分级响应策略——单门异常仅锁定本工位，不连锁全线停机。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>电气控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>安全回路集成</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>故障安全原则</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>请简述在工业通信中，主站向从站发送数据时，数据交换的基本触发方式是什么？</t>
+          <t>PLC与运动控制</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>在自动化工程师日常工作中，主站向从站发送数据，最基础的触发方式是主站主动发起——也就是主站按设定周期或条件，自主决定何时把指令、参数或控制字发给从站，从站不主动请求，只响应接收。</t>
+          <t>工业通信</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>实际产线调试和维护中，常用三种触发方式：一是固定周期轮询，主站定时扫描每个从站，稳定性高但响应有延迟；二是事件驱动触发，比如主站收到传感器信号或操作指令后立即发数据，实时性好但需额外逻辑判断；三是混合模式，用周期通信传常规状态，用事件触发传急停、复位等关键指令。综合来看，混合模式最常用——既保障运动控制的节奏感，又兼顾突发动作的及时性，符合产线柔性切换和快速启停的实际需求。</t>
+          <t>主从站数据交换原理</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1个异常情况概要：主站发出数据后，从站无响应。具体情况是伺服驱动器未更新位置指令，导致轴运动滞后或停顿。解决思路是先确认主站输出缓冲区是否已刷新、再检查从站通信使能状态及本地急停回路是否导通，最后验证总线终端电阻和屏蔽接地是否可靠。1个复杂问题概要：多轴协同场景下，主站对不同从站的指令发出时刻存在微秒级偏差。具体问题是电子齿轮同步精度下降，影响装配节拍一致性。解决思路是启用主站内置的时间戳同步机制，统一所有从站的通信起始相位，并通过现场实测各轴反馈延时，反向补偿主站指令偏移量。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>PLC与运动控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>工业通信</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>主从站数据交换原理</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>请简单说说在主从站通信中，主站读取从站数据的过程，其数据流向是怎样的？</t>
+          <t>PLC与运动控制</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>主站主动发起读取请求，通过通信总线将指令发送至从站；从站收到后解析地址与数据长度，从自身内存映射区提取对应数据，再沿原路径返回给主站；整个过程是单向触发、双向传输，数据流向为主站→从站（请求），从站→主站（响应）。</t>
+          <t>工业通信</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>实际工程中常用三种方式：一是周期性轮询，主站按固定节拍依次读取各从站，实时性可控但存在延迟累积；二是事件触发式读取，仅在从站状态变化时上报，节省带宽但依赖从站本地判断逻辑，对主站调度能力要求高；三是混合模式，关键变量用高速周期通道，非关键量用变化上报，兼顾效率与可靠性。综合产线稳定性、调试便利性和设备兼容性，混合模式在当前产线升级项目中最常用，既避免轮询冗余，又规避纯事件机制带来的诊断盲区。</t>
+          <t>主从站数据交换原理</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1个异常情况概要：主站收不到从站响应。具体情况：通信链路物理正常，但主站持续超时，常见于从站地址配置错误或寄存器映射未使能。解决思路：先确认主从站地址与功能码一致，再检查从站本地是否已启用对应数据区的通信使能位，最后验证主站扫描周期是否短于从站最小响应时间。1个复杂问题概要：多从站共用同一物理总线时读取数据错位。具体问题：某伺服驱动器返回的数据被误认为是另一台PLC的反馈值，导致运动轴位置异常跳变。解决思路：逐站核对通信帧头标识与设备ID绑定关系，强制启用从站唯一应答标识校验，并在主站侧增加数据源身份校验逻辑，确保每帧响应与发起请求的从站严格一一对应。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>PLC与运动控制</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>工业通信</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>主从站数据交换原理</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>请简述Profinet通信中实时数据传输所依赖的底层网络技术。</t>
+          <t>工业通信</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Profinet实时数据传输不依赖传统以太网的通用转发机制，而是通过在标准以太网物理层和数据链路层基础上，由PLC和现场设备协同实现确定性调度，核心是利用交换机端口硬件级时间戳与控制器统一时钟同步，确保I/O数据在固定微秒级窗口内完成收发。</t>
+          <t>现场总线应用</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>实际工程中主要有三种实现方式：一是使用支持IEEE 802.1AS时间同步和802.1Qbv时间敏感流调度的工业交换机，精度高、扩展性强，但对设备选型和组态要求严格；二是采用Profinet RT协议，在普通商用交换机上靠控制器软件调度+报文优先级标记，成本低、兼容性好，但仅适用于中小规模产线；三是结合TSN增强型控制器与边缘侧时间门控，适合新老设备混用场景。综合来看，当前制造业产线升级中，优先选用支持TSN基础特性的国产工业交换机配合主流PLC，兼顾确定性、可维护性和备件可持续性。</t>
+          <t>Profinet通信机制</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1个异常情况概要：实时通道周期性超时。具体情况：某伺服轴位置反馈数据连续多个周期未到达PLC，但网络连通性正常、LED指示灯无告警。解决思路：先确认控制器与设备间时钟同步状态是否丢失，再检查交换机端口是否因广播风暴触发了优先级队列溢出，最后核查设备固件是否存在已知的时间戳处理缺陷。1个复杂问题概要：多协议共网干扰导致实时抖动增大。具体问题：产线同时运行Profinet实时I/O、OPC UA信息采集和视频监控流，造成周期性延迟跳变。解决思路：在核心交换机启用基于流的带宽预留和入口整形，将实时流量绑定到专用硬件队列，并将非实时业务迁移至物理隔离的副网段，避免控制器侧软件协议栈争抢中断资源。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>工业通信</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>现场总线应用</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Profinet通信机制</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>在Modbus RTU通信中，功能码03读取保持寄存器时，报文中的起始地址字段对应的是哪种地址格式？</t>
+          <t>工业通信与数据集成</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>起始地址字段对应的是从0开始的十六进制偏移地址，也就是PLC内部保持寄存器的物理存储序号，不包含设备地址、功能码或寄存器类型前缀。</t>
+          <t>Modbus通信应用</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>实际工程中常用三种映射方式：一是直接按PLC内存布局填入起始偏移值，响应快但需查手册，易出错；二是通过组态软件自动生成地址映射表，兼容性好但依赖配置一致性；三是用标准化地址标签绑定机制，在HMI或SCADA里统一管理，维护性最强但需前期建模投入。综合时效性与现场适配性，第二种方式最常用——即在组态工具中选择对应PLC型号后，由软件自动将‘40001’这类逻辑地址转换为报文所需的十六进制偏移值，既避免人工换算错误，又满足产线快速调试需求。</t>
+          <t>寄存器地址映射</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1个异常情况概要：读取返回异常数据或超时。具体情况：起始地址填成十进制逻辑地址（如40001）而非十六进制偏移（如0x0000），导致访问到非保持寄存器区域甚至非法内存。解决思路：现场优先核对PLC编程软件中寄存器地址栏显示的实际偏移值，并用串口调试工具抓包验证报文字段是否为两位十六进制数。1个复杂问题概要：多品牌PLC混用时地址映射不一致。具体问题：同一逻辑地址在不同厂商PLC中对应的偏移值不同，例如某国产PLC把40001映射为0x0000，而进口PLC可能映射为0x0001。解决思路：建立跨品牌地址映射对照表，嵌入到自动化系统集成方案文档中，并在项目启动阶段完成三方（PLC厂商、上位机厂商、产线集成方）联合地址校验测试。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>工业通信与数据集成</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Modbus通信应用</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>寄存器地址映射</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Modbus规范里，输入寄存器的地址范围用十进制表示时，一般从多少开始编号？</t>
+          <t>工业通信与数据集成</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>输入寄存器的十进制地址编号通常从四万零零零一，也就是40001开始。</t>
+          <t>Modbus通信应用</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>在制造业产线自动化项目中，工程师配置PLC与传感器、智能仪表通信时，需准确映射输入寄存器地址。常见做法有三种：一是严格按Modbus标准从40001起始编号，兼容性最好，适用于绝大多数国产和进口PLC及HMI；二是部分厂商设备支持偏移寻址，允许从40000开始，但容易引发跨品牌通信误读；三是通过配置软件自动映射，虽降低人工出错率，但调试阶段难以快速定位地址偏差。综合来看，坚持从40001起始编号是最稳妥的选择，既符合现场维护人员的习惯，也避免因地址错位导致数据读取异常，尤其在多品牌设备混用的产线改造项目中优势明显。</t>
+          <t>寄存器地址映射</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1个异常情况概要：读取到的数据始终为零或乱码。具体情况：实际接线和功能码正确，但HMI或SCADA显示输入寄存器值全为零。解决思路：立即核查地址是否误用了保持寄存器的30001起始规则，或PLC侧未启用对应通道的模拟量采集任务。1个复杂问题概要：同一台仪表在不同品牌PLC上地址解析不一致。具体问题：某温度模块在A品牌PLC中40001对应通道1，在B品牌中却对应通道2。解决思路：不依赖设备默认地址映射，而是以设备手册标注的‘寄存器索引’为准，在PLC编程软件中手动建立地址偏移表，并在项目文档中固化该映射关系，确保调试与交接可追溯。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>工业通信与数据集成</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Modbus通信应用</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>寄存器地址映射</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>请简述Modbus协议中功能码06的作用。</t>
+          <t>工业通信与数据集成</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>功能码06用于向单个从站设备写入一个16位寄存器的数值，常用于设置PLC或智能仪表中的控制参数，比如设定温度目标值、速度给定值或启停指令。</t>
+          <t>Modbus通信应用</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>在产线调试和日常维护中，工程师通常有三种常用方式实现功能码06写入：一是通过HMI界面直接下发，优点是操作直观、无需编程，但依赖HMI配置完整性，一旦画面未绑定对应地址就失效；二是用PLC主站程序周期性调用Modbus写指令，稳定性高、可集成逻辑判断，但需占用PLC资源且修改参数需停机下载；三是借助调试工具如串口助手或SCADA工程软件临时写入，响应快、灵活度高，但不具备持续监控与异常反馈能力。综合来看，在制造现场最稳妥的做法是采用PLC主站程序控制，既保障写入可靠性，又能与安全联锁、状态校验等环节联动。</t>
+          <t>功能码识别</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>1个异常情况概要：写入后从站无响应或返回异常码。具体情况：PLC发送功能码06后，从站返回0x02（非法地址）或0x03（非法数据值），常见于寄存器地址映射错误或目标设备处于禁止写入状态。解决思路：先确认从站手册中该地址是否支持写操作，再核对设备当前运行模式（如是否处于本地锁定、参数保护启用状态），最后检查主站发出的地址偏移是否与从站实际寄存器编号一致。1个复杂问题概要：多台设备共用同一Modbus总线时，单次写入引发连锁误动作。具体问题：某台变频器写入频率设定值后，相邻伺服驱动器因地址错位或缓存未刷新，误读该值并执行错误动作。解决思路：严格按设备手册划分地址段，写入前增加设备ID校验与写使能信号同步，关键参数写入后必须读回验证，并在PLC程序中加入最小间隔延时与失败重试机制。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>工业通信与数据集成</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Modbus通信应用</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>功能码识别</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>当设备手册标注某参数映射到保持寄存器40001时，这个‘40001’属于Modbus的哪种地址表示方式？</t>
+          <t>工业通信与数据集成</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>这是Modbus协议中常用的‘功能码+偏移量’混合型地址表示法，其中‘40001’代表功能码03（读保持寄存器）所对应的首地址，数字中的首位‘4’表示寄存器类型为保持寄存器，后四位‘0001’表示从第1个寄存器开始计数，即实际物理地址偏移为0。</t>
+          <t>Modbus通信应用</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>在自动化工程师日常调试中，主要有四种处理方式：一是直接按手册地址填入PLC配置界面，优点是最快上手，但易忽略地址转换逻辑；二是将40001减去40001得到偏移0再填入，通用性强，但需人工换算，现场易出错；三是使用组态软件内置的地址解析功能自动识别前缀，时效性好且容错率高，当前主流HMI和PLC编程环境都支持；四是通过通信诊断工具实时抓包比对地址映射，精度最高但耗时长，仅用于疑难问题定位。综合来看，第三种方式最适配产线快速部署与多品牌设备兼容需求。</t>
+          <t>寄存器地址映射</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1个异常情况概要：PLC读取40001地址返回无效数据。具体情况：设备手册标40001，但实际寄存器起始地址为40000或40002，导致偏移错位。解决思路：先确认设备厂商是否采用‘1起始’或‘0起始’惯例，再用万用表级通信测试仪验证真实响应地址。1个复杂问题概要：同一台设备在不同PLC品牌中对40001的解析结果不一致。具体问题：某国产PLC将40001默认转为偏移0，而进口PLC要求手动勾选‘Modbus地址兼容模式’才生效。解决思路：统一在项目前期建立《设备通信接口规范表》，明确每台设备的地址解析规则，并固化到工程模板中，避免后期重复排查。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>工业通信与数据集成</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Modbus通信应用</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>寄存器地址映射</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>请简述Modbus协议中功能码01的作用。</t>
+          <t>工业通信与数据集成</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>功能码01用于读取从站设备的多个连续线圈状态，也就是读取开关量输出点的通断情况，比如PLC输出端口、继电器触点或电磁阀等二值信号的状态。</t>
+          <t>Modbus通信应用</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>在自动化产线调试和日常运维中，工程师常用三种方式实现功能码01的调用：一是通过PLC内置Modbus主站指令直接轮询，响应快但占用CPU资源较多；二是借助HMI或SCADA系统内置通信模块发起请求，配置灵活、便于监控，但依赖上位软件稳定性；三是使用工业网关做协议转换后统一采集，适合多品牌设备集成，但增加中间环节可能引入延迟。综合考虑实时性、可维护性和产线兼容性，PLC原生指令方式最常用，尤其在对响应时间敏感的包装、装配工位中。</t>
+          <t>功能码识别</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1个异常情况概要：读取返回数据全为0或乱码。具体情况：现场常见于从站地址设置错误、波特率不匹配或RS485接线A/B反接。解决思路：先确认主从站地址与波特率参数一致，再用万用表测A/B线间电压是否在±200mV以上，最后逐段断开分支线路排查终端电阻缺失或共模干扰。1个复杂问题概要：同一主站轮询多个从站时部分站点偶发超时。具体问题：产线设备分布广、电缆长度差异大，导致信号衰减不均，叠加变频器等干扰源影响边沿识别。解决思路：分段加装RS485中继器，为长距离从站单独配置更宽松的超时阈值，并在干扰强区域改用带屏蔽双绞线且单点接地。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>工业通信与数据集成</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Modbus通信应用</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>功能码识别</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>若主站向从站发送功能码16的批量写寄存器请求，但收到的功能码为81的响应，这表明从站在处理该请求时遇到了哪类典型问题？请简单说说。</t>
+          <t>工业通信与数据集成</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>这表明从站在执行功能码16请求时发生了异常，主动返回了异常响应——功能码81是功能码16加0x80的结果，属于Modbus协议约定的异常应答机制，说明从站识别到了请求，但因某种原因无法正常完成写操作。</t>
+          <t>Modbus通信应用</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>在产线调试和设备联调中，工程师通常会从三个方向排查：一是检查从站寄存器地址范围是否越界，比如请求写入的保持寄存器起始地址或数量超出了PLC或仪表实际支持的区域；二是确认从站当前运行状态是否允许写入，例如设备处于急停锁定、本地手动模式或参数保护启用状态；三是核查通信链路稳定性与从站响应超时设置是否匹配。其中，优先验证地址合法性最高效，因为地址错误占比超六成，且可在不中断设备运行的前提下通过配置工具快速比对；而状态类限制需结合现场操作模式综合判断，时效性略低但更贴近真实工况。</t>
+          <t>功能码识别</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1个异常情况概要：从站返回81但无其他日志提示。具体情况：PLC程序未启用对应寄存器区的写权限，或HMI/上位机配置了写保护标志位。解决思路：进入从站设备配置界面，核对寄存器区读写属性设置，并临时关闭软件级写保护进行验证。1个复杂问题概要：同一功能码16请求在部分时段成功、部分时段返回81。具体问题：从站CPU负载过高导致响应超时后触发异常应答，而非逻辑错误。解决思路：观察从站运行周期与通信间隔匹配度，缩短主站重试间隔或优化从站扫描周期，在不影响控制逻辑前提下释放通信资源窗口。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>工业通信与数据集成</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Modbus通信应用</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>功能码识别</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>请简述在夹治具设计中，什么是定位基准？</t>
+          <t>机械结构与设备机构</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>定位基准是指在夹治具中，用来确定工件在加工或装配过程中空间位置的、实际接触并约束工件自由度的物理表面、边、孔或轴线等结构要素。</t>
+          <t>夹治具定位理解</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>在自动化产线现场，工程师常选三类定位基准：一是工件已加工的高精度面或孔，稳定性好但依赖前道工序质量；二是工件毛坯上的铸造/冲压基准面，适配大批量生产但重复定位精度偏低；三是增设工艺凸台或定位销孔，需额外机加，但能统一各工位基准，提升节拍一致性。综合来看，优先选用工件自身高精度已加工特征作为基准最经济可靠，前提是该特征在上游工序中具备过程能力且状态稳定，避免因基准迁移导致整线调试反复。</t>
+          <t>定位基准选择</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1个异常情况概要：基准面存在轻微磕碰或油污未清除。具体情况：工件基准面局部损伤或残留冷却液，导致夹紧后微倾，引发后续视觉引导偏差或机器人抓取偏移。解决思路：在夹具入口增加轻触式清洁气吹+接触式基准面平整度预检，由PLC联动判定是否允许进站。1个复杂问题概要：多工位协同作业下基准不统一。具体问题：同一工件在焊接、搬运、检测等不同工位使用不同基准定位，造成累积误差超限，影响终检合格率。解决思路：以总装或关键尺寸所在工位为基准源，反向校准其余工位夹具的安装基准，通过激光跟踪仪实测各工位基准点空间关系，用机械调整+软件坐标系偏移补偿双轨校正。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>机械结构与设备机构</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>夹治具定位理解</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>定位基准选择</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>请简述重复定位精度在夹治具设计中的基本含义。</t>
+          <t>机械结构与设备机构</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>重复定位精度，指的是同一套夹治具在多次装夹同一工件时，工件相对于夹治具基准面或定位元件所达到的位置一致性程度。它反映的是夹治具自身结构刚性、定位元件配合稳定性以及装配重复性的综合表现，不涉及工件本身尺寸公差或机床运动误差。</t>
+          <t>夹治具定位理解</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>在自动化产线现场，提升重复定位精度主要有四种常用方法：一是采用过定位+自适应补偿结构，比如带弹性浮动销的双销定位，能吸收微小装配偏差，但对零件表面质量敏感；二是使用高精度可调定位块，通过微调螺钉实现现场快速标定，调整效率高但长期使用易松动；三是引入一体式铸铁基座与嵌入式硬质合金定位销，热变形小、耐磨性好，初期成本高但寿命长、维护少；四是加装简易机械式复位检测机构，如弹簧压紧+行程开关反馈，可实时判断定位是否到位。综合来看，第三种方案在大批量自动化产线中可靠性最高、长期运行一致性最好，是当前主流产线的首选。</t>
+          <t>重复定位精度</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>1个异常情况概要：夹治具重复定位精度突然变差。具体情况：连续多批次工件首件检测合格，但后续加工中出现位置偏移超差，且无明显磨损或松动。解决思路：优先排查定位销根部基体是否存在隐性裂纹或基座安装螺栓预紧力衰减，用扭矩扳手按工艺要求复拧并做红丹接触验证。1个复杂问题概要：异形薄壁件在自动上下料过程中重复定位波动大。具体问题：机械手抓取后放入夹治具时产生微小弹性变形，导致每次压紧后基准面回弹量不一致。解决思路：改用分段式柔性压紧+顺序锁紧策略，先以低压力初定位，再通过气缸延时分级增压，同时在关键支撑点增设微型应变反馈单元辅助闭环判断，确保每次压紧状态可复现。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>机械结构与设备机构</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>夹治具定位理解</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>重复定位精度</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>请简述防错结构设计在工装夹具中主要实现什么功能？</t>
+          <t>非标设备与机械结构</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>防错结构设计在工装夹具中，核心是防止操作人员或设备因误装、反装、漏装、错位等人为或机械偏差导致后续加工或装配出错，从而在物理层面提前拦截错误发生，保障单件流作业的准确性和过程稳定性。</t>
+          <t>工装夹具结构</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>目前主流有四类实现方式：一是定向槽/键槽匹配，靠形状唯一性限制零件朝向，结构简单但对公差敏感；二是不对称定位销或缺口，成本低、免维护，但需同步校验夹具与零件的配合一致性；三是带反馈的机械自锁机构，比如到位即触发微动开关，能联动设备停机，可靠性高但增加调试复杂度；四是嵌入式限位块组合，通过空间干涉强制归正，适应性强但占用空间大。综合来看，在自动化产线中，‘不对称定位+机械限位’组合方案最常用——它不依赖电气信号，响应快、故障率低，且便于快速换型验证。</t>
+          <t>防错结构设计</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1个异常情况概要：夹具防错结构因长期磨损导致间隙增大。具体情况：定位销或导向面磨损后，零件仍能勉强装入但姿态偏移，设备未报警却持续加工不良品。解决思路：将关键防错部位纳入日常点检项，用标准塞规定期核查配合间隙，并设定累计运行小时数触发强制更换周期。1个复杂问题概要：同一夹具需兼容多代相似零件。具体问题：不同版本零件在定位孔距或外形上存在微小差异，原有防错结构无法兼顾，强行共用易引发误判。解决思路：采用模块化可调定位基座，配合快换式防错镶件，通过物理结构调整而非软件逻辑变更来适配差异，确保防错功能始终由结构本身承载。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>非标设备与机械结构</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>工装夹具结构</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>防错结构设计</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>请简单说说什么是‘接触式防错’，它依靠什么物理特性来防止操作错误？</t>
+          <t>非标设备与机械结构</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>接触式防错是一种通过工装夹具的物理结构强制约束操作顺序或装配方向的防错方式。它不依赖传感器或程序判断，而是依靠零件与夹具之间真实的、不可绕过的机械接触关系，来确保只有正确姿态、正确方向、正确数量的工件才能被装入或定位到位。</t>
+          <t>工装夹具结构</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>在非标自动化设备现场，常见的接触式防错结构有四种：一是单向导向槽，靠不对称截面限制旋转和翻转，成本低但对公差敏感；二是异形定位销，利用销孔形状差异实现唯一匹配，可靠性高但加工精度要求严；三是限位凸台+缺口配合，结构简单、维护方便，但长期磨损后易失效；四是斜面自校正导向，能容忍轻微偏移并自动归正，适合节拍快的产线，但设计复杂度高。综合来看，异形定位销方案在量产稳定性、寿命和验证便捷性上最平衡，是当前主流产线首选。</t>
+          <t>防错结构设计</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1个异常情况概要：夹具定位面因长期使用出现微磨损。具体情况：原本严丝合缝的异形销孔配合间隙变大，导致错误方向的工件也能勉强压入，防错功能失效。解决思路：将定位面改为可更换式嵌入块，并在点检清单中加入间隙量目视确认项，每5000次循环强制更换。1个复杂问题概要：多品种共用夹具时防错结构冲突。具体问题：同一夹具需兼容A/B两种外形相近但关键特征相反的工件，单一接触结构无法同时满足双向防错。解决思路：采用模块化快换定位基座，通过预设的机械编码接口自动识别当前型号，并触发对应位置的可伸缩限位块动作，实现物理结构的按需切换。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>非标设备与机械结构</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>工装夹具结构</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>防错结构设计</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>在非标设备中，升降移载机构常使用丝杠或同步带作为传动方式，请简述这两种方式在实现垂直方向精准定位时，各自依赖的关键机械结构特征。</t>
+          <t>非标设备与机械结构</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>丝杠方式依赖高精度梯形丝杠或滚珠丝杠本体的导程精度、螺母与丝杠的预紧状态及轴向刚性支撑结构；同步带方式依赖张紧后的同步带本体抗拉变形能力、带轮齿形啮合稳定性、以及带轮轴系的径向跳动与安装同轴度。</t>
+          <t>机械执行机构</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>丝杠方案优势是重复定位精度高、刚性强、断电自锁性好，适合负载大、行程短、精度要求严的场景，但成本高、速度受限、长行程易下垂；同步带方案优势是速度快、行程灵活、成本低、惯量小，适合轻载、中长行程、节拍快的场合，但存在弹性变形和带轮跳动带来的累积误差，需额外补偿。综合来看，在非标自动化产线中，若定位精度要求优于±0.05毫米且负载超30公斤，优先选预紧滚珠丝杠配双支撑轴承结构；其余多数升降移载工位，选用高模量聚氨酯同步带配双侧张紧轮与带轮跳动≤0.02毫米的铝制带轮更经济可靠。</t>
+          <t>升降移载机构</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1个异常情况概要：同步带在垂直安装时突发打滑。具体情况：设备运行数月后，带轮表面轻微磨损叠加环境温湿度变化，导致摩擦系数下降，重力方向启动瞬间带齿跳齿。解决思路：改用带背胶防滑层的同步带，加装独立张紧力监测弹簧片，并在PLC逻辑中嵌入启停前的带张力确认环节。1个复杂问题概要：丝杠升降机构在多点频繁启停下出现微米级定位漂移。具体问题：伺服电机闭环反馈正常，但实际位置随温度升高缓慢偏移0.03～0.08毫米。解决思路：排查丝杠支撑端轴承游隙是否因热膨胀增大，改用角接触轴承配合理预紧，同时在机械设计阶段预留丝杠轴向热伸长补偿间隙，并在调试阶段做温度-位移标定补偿曲线。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>非标设备与机械结构</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>机械执行机构</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>升降移载机构</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>请简述PLC如何读取视觉系统输出的检测结果数据？</t>
+          <t>机器视觉应用</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PLC通过标准工业通信方式，接收视觉系统发出的检测结果信号。这些信号通常是合格/不合格判定、位置偏移量、缺陷类型等结构化信息，以开关量、模拟量或数字字的形式，按约定地址写入PLC的输入映像区或指定寄存器中。</t>
+          <t>视觉系统集成</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>实际工程中常用三种交互方式：一是硬接线方式，用光电隔离的数字信号线传输OK/NG结果，响应快、抗干扰强，但扩展性差、布线成本高；二是基于Modbus TCP协议的以太网通信，视觉系统作为从站提供结果寄存器，PLC主站周期性读取，配置简单、点位灵活，但受网络延迟和交换机性能影响；三是采用EtherNet/IP或PROFINET等实时工业以太网协议，支持带时间戳的结果同步与状态反馈，适合高速产线，但对设备兼容性和网络调试能力要求更高。综合来看，在当前主流产线中，Modbus TCP是平衡开发效率、维护便利性和实时性的首选方案。</t>
+          <t>视觉与PLC交互方式</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>异常情况概要：PLC偶尔读不到最新检测结果。具体情况：视觉系统已更新结果寄存器，但PLC连续两次扫描都读到旧值。解决思路：先确认PLC通信周期是否大于视觉系统结果刷新间隔，再检查视觉端是否启用‘结果锁存’或‘上升沿触发’机制，必要时在PLC侧增加读取确认逻辑或超时重读机制。复杂问题概要：多工位共用同一台视觉系统时，PLC无法区分结果归属。具体问题：多个工位触发拍照后，视觉系统按队列返回结果，但PLC收不到对应工位标识。解决思路：要求视觉系统在返回数据中嵌入工位ID字段，PLC通过解析该字段匹配当前工序状态；若视觉不支持，需在PLC侧建立触发-应答时序表，结合IO触发信号与通信时间戳做双向校验。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>机器视觉应用</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>视觉系统集成</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>视觉与PLC交互方式</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>请简述故障复现的基本目的。</t>
+          <t>调试与验收</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>故障复现的基本目的，是在自动化产线或设备调试与验收阶段，通过可控、可重复的方式，让已发生的异常现象再次出现，从而为后续的故障定位、原因分析和验证整改效果提供可靠依据。</t>
+          <t>故障诊断</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>在制造业现场，常用方法有三种：一是按原始工况回溯操作，优势是真实性强、无需额外配置，但耗时长且可能受产线节拍约束；二是用PLC仿真环境加载历史数据触发逻辑分支，响应快、安全性高，但对信号完整性依赖强，无法覆盖传感器物理失效类问题；三是通过HMI或调试终端强制注入典型异常条件，如模拟急停信号丢失、伺服使能中断等，时效性最好、便于分段隔离，但需确保不破坏当前运行状态。综合来看，第三种方法在调试与验收场景中适用性最广——它既满足快速闭环验证需求，又符合电气安全规范下‘单点可控、风险隔离’的操作原则。</t>
+          <t>故障复现与验证</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>1个异常情况概要：复现失败但故障实际存在。具体情况：操作步骤完全复刻，设备却无异常响应。解决思路：先确认是否因设备状态重置（如伺服清零、气压归零）导致触发条件消失；再检查外围信号链路（如光电开关遮挡状态、安全继电器自锁释放）是否被无意恢复。1个复杂问题概要：故障仅在特定生产节奏下偶发。具体问题：高速连续运行15分钟以上才出现通讯超时，单次动作无法触发。解决思路：采用‘时间压力+负载叠加’策略——在调试模式下模拟节拍加速，并同步加载额定负载，同时启用PLC内置周期性诊断日志，聚焦捕捉总线响应延迟趋势，而非等待错误报警产生。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>调试与验收</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>故障诊断</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>故障复现与验证</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>请简述GRR在质量控制中代表什么含义？</t>
+          <t>调试与验收</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GRR是测量系统分析中的一个核心指标，全称是量具重复性与再现性，它用来评估一套测量系统——比如三坐标、激光跟踪仪或者产线自动检测工装——对同一零件多次测量时，数据波动有多大比例来自测量工具自身，而不是零件真实差异。</t>
+          <t>精度验证</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>在自动化产线调试与验收阶段，我们常用三种方法做GRR验证：一是嵌入式传感器直采法，把测量单元集成到设备本体里，时效性高但受安装刚性影响大；二是离线标准件比对法，用高精度标准件反复测试，结果稳定但耗时长；三是在线动态抽样法，结合PLC触发与视觉/位移传感器同步采集，兼顾效率和代表性。综合来看，在线动态抽样法最适合当前主流自动化产线的验收节奏——它不打断节拍，能覆盖夹具定位、伺服到位、温度漂移等真实工况，数据可直接关联设备参数台账。</t>
+          <t>GRR与CPK含义</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>1个异常情况概要：GRR突然超标。具体情况：某电池模组压装站验收时GRR从12%飙升至45%，排查发现不是传感器故障，而是新换的气动夹具底座螺栓预紧力不足，导致测量过程中微幅晃动。解决思路：立即停测，复核夹具基座刚性与地脚固定状态，用扭矩扳手按工艺要求重紧，并加入夹具振动频谱监测作为GRR前置检查项。1个复杂问题概要：多工位串联测量系统的GRR耦合干扰。具体问题：总成装配线含5个自动测量工位，单站GRR均合格，但整机尺寸链CPK持续偏低。解决思路：开展跨工位测量路径一致性分析，重点校验各站坐标系原点传递误差和基准转换逻辑，采用‘主基准工装贯通校准’方式统一溯源，而非孤立验证每站。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>调试与验收</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>精度验证</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>GRR与CPK含义</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>某自动装配站的定位精度要求为±0.1毫米，实测数据计算出的CPK值为1.2，请简述这个数值说明当前过程满足规格要求的程度如何。</t>
+          <t>调试与验收</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CPK值为1.2，说明当前装配过程的中心偏移和离散程度综合表现处于可接受范围，但尚未达到高稳定水平；从精度验证角度看，它反映的是设备在实际运行中持续产出合格定位结果的能力，不是单次调试结果，而是基于多批次、多周期实测数据得出的过程能力指标。</t>
+          <t>精度验证</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>在自动化产线调试与验收阶段，常用三种方式验证CPK：一是用标准件重复打点采集30组以上定位数据，优势是操作简单、现场可快速实施，缺点是对环境扰动敏感；二是结合激光跟踪仪做动态轨迹采样，能捕捉伺服响应波动，但成本高、耗时长；三是嵌入式采集PLC位置反馈与编码器脉冲差值，实时性强、复现性好，需提前配置信号接口。综合来看，第三种方法最适合产线现场验收——既能保障时效性，又能覆盖运动控制全链路误差源，包括机械间隙、伺服跟随滞后和传感器延迟。</t>
+          <t>GRR与CPK含义</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>1个异常情况概要：CPK达标但首件/末件超差。具体情况：连续运行中中间段数据稳定，但启停阶段定位偏差突增。解决思路：排查伺服参数中的加减速斜率与惯量匹配是否合理，重点检查调试时是否仅用稳态数据建模，未覆盖启停过渡工况。1个复杂问题概要：CPK值合格但不同班次结果差异大。具体问题：白班数据CPK为1.3，夜班降为0.9。解决思路：不是单纯重测，而是核查两班次使用的夹具基准面磨损状态、气压稳定性及温控条件是否一致，优先确认测量系统GRR是否在班次切换后发生漂移。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>调试与验收</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>精度验证</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>GRR与CPK含义</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>请简述在设备交付前，工厂内部完成的验收测试和客户现场完成的验收测试，各自主要验证什么内容？</t>
+          <t>调试与验收</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>工厂内部验收测试，也就是出厂验收测试，核心是验证设备是否按合同和技术协议要求，在受控环境下完成了全部功能、安全和接口匹配；客户现场验收测试，是在实际产线环境中开展的，重点验证设备与客户现有系统、工艺节拍、物料流和人员操作的真实适配性。</t>
+          <t>验收管理</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>常用方法有三类：一是纯功能点检表驱动测试，执行快但易漏联调风险；二是模拟工况带载运行，覆盖全面但准备周期长；三是分阶段交叉验证，即先做单机空载、再联线空跑、最后带料试产，兼顾时效与完整性，是当前制造业自动化工程师最常采用的平衡方案。其中第三种方法在交付压力与质量保障之间取得最优折中，既避免返工又支撑客户签字确认。</t>
+          <t>FAT与SAT区别</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>1个异常情况概要：客户现场SAT时发现设备节拍不达标。具体情况：设备在工厂测试满足理论节拍，但到客户现场后因输送线定位偏差、气压波动或上下游设备响应延迟，导致整线循环时间超差。解决思路：快速锁定瓶颈环节，用秒表+过程录像回溯关键动作时序，协同客户调整信号触发逻辑或缓冲策略，不改动硬件前提下优化时序配合。1个复杂问题概要：客户既有PLC系统与新设备通信协议不兼容。具体问题：客户老产线使用私有扩展指令，新设备控制器默认只支持标准协议。解决思路：由自动化工程师牵头组织协议映射方案评审，通过配置中间通信模块或重写部分IO映射逻辑，在不升级客户原有控制系统前提下实现信号级互通。</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>调试与验收</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>验收管理</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>FAT与SAT区别</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>预防性维护与故障后维修最根本的区别体现在哪个环节？</t>
+          <t>产线优化与运维</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>最根本的区别体现在维修决策的触发时机：预防性维护是依据设备运行状态、使用周期或历史规律，在故障发生前主动安排维护；故障后维修则是在设备已经停机、功能失效、产线中断后才启动响应。</t>
+          <t>设备运维管理</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>在自动化产线现场，常用三种触发方式：一是按固定时间周期执行，比如每运行500小时停机点检，优点是计划性强、组织简单，但容易造成过度维护或漏检；二是基于传感器数据的趋势判断，比如振动、温度、电流等连续监测，能动态反映退化趋势，时效性和针对性强，但依赖信号质量和分析模型稳定性；三是结合OEE统计与历史故障模式做风险预测，兼顾产线节拍和备件库存，整体协同性好，但需要跨系统数据整合能力。综合来看，第二种——基于实时运行参数的趋势判断方式，在当前主流产线中时效性与实用性平衡最好，既避免盲目停机，又守住关键设备可靠性底线。</t>
+          <t>预防性维护概念</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>1个异常情况概要：传感器信号漂移导致趋势误判。具体情况：某输送线电机驱动端振动传感器因接线松动产生虚假高频波动，系统误判为轴承早期磨损而提前报修，实际设备状态正常。解决思路：先比对同型号电机多台设备的同类信号基线，再现场复位传感器并做短时空载验证，确认信号真实性后再更新阈值模型。1个复杂问题概要：多设备耦合退化下的维护窗口冲突。具体问题：包装段三台伺服压盖机存在机械联动关系，各自预测的维护时间点集中在同一班次，集中停机会导致整线停产超30分钟。解决思路：以整段产线最小节拍为约束，把单机维护需求转化为资源调度问题，优先保障瓶颈工位，非瓶颈设备微调维护时机，并同步协调备件与技工排班，实现‘错峰+保产’双目标。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>产线优化与运维</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>设备运维管理</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>预防性维护概念</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>请简述MTBF这个指标代表什么含义？</t>
+          <t>设备诊断改善</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MTBF是平均故障间隔时间，指自动化产线中可修复设备在两次相邻故障之间正常运行的平均时长，用于量化设备持续稳定工作的能力。</t>
+          <t>设备可靠性分析</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>在自动化工程师日常工作中，常用三种方式获取MTBF：一是从PLC历史报警日志中自动提取停机事件并计算间隔；二是通过SCADA系统对接设备运行状态信号，实时统计无故障运行时段；三是结合预防性维护记录人工校准异常停机原因。第一种方法时效性高、数据源原生可靠，但需排除误报警干扰；第二种覆盖全面、支持趋势分析，但依赖信号采集完整性；第三种准确性高，但耗时且难标准化。综合来看，优先采用PLC日志自动提取法，并辅以维护记录交叉验证，既保障时效又兼顾工程判据。</t>
+          <t>MTBF指标含义</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1个异常情况概要：MTBF数值突然大幅升高。具体情况：并非设备变可靠，而是故障未被PLC正确识别或报警被人为屏蔽，导致故障漏记。解决思路：核查PLC报警触发逻辑是否覆盖典型失效模式，比对现场停机记录与系统日志的一致性，重点检查急停、过载、通信中断等关键信号的采集有效性。1个复杂问题概要：同类设备MTBF差异显著。具体问题：同一型号伺服驱动器在不同工位表现迥异，无法归因于单一因素。解决思路：分层排查——先确认安装环境（如散热、振动、电源波动）是否一致；再比对控制策略（启停频次、加减速曲线、负载率）差异；最后调取各台设备的运行参数快照，识别是否存在隐性超限运行，从而定位真实劣化诱因。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>设备诊断改善</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>设备可靠性分析</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>MTBF指标含义</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>请简单说说故障树中的‘基本事件’指的是哪类事件？</t>
+          <t>故障诊断与可靠性</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>基本事件是指在故障树分析中，不能再向下分解、也不需要进一步拆解的底层故障点。它对应自动化产线中某个具体硬件组件或控制环节发生的、可直接观测或测量的失效行为，比如一个光电开关突然无信号输出、某台伺服驱动器报过流故障、PLC某个输入模块失电等。</t>
+          <t>故障根因分析</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>在产线故障排查中，常用三种方式定位基本事件：一是基于历史维修记录做经验归集，优点是响应快但覆盖有限；二是结合设备IO状态与报警日志做实时比对，能准确定位但依赖信号完整性；三是通过PLC程序逻辑反向追踪触发条件，全面性好但要求工程师熟悉控制逻辑。综合来看，第二种方法最常用——它以现场实际信号状态为依据，在产线停机窗口短、复机压力大的前提下，既能快速锁定失效点，又避免过度依赖主观经验或程序细节。</t>
+          <t>故障树拆解</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>1个异常情况概要：基本事件被误判为中间事件。具体情况：例如把‘气缸未到位’当作基本事件，但实际上它由电磁阀动作失败、气压不足、限位开关误触发等多个原因导致，若不继续拆解就可能漏掉真实根因。解决思路：立即回溯该事件是否具备独立可观测性，检查其上游是否有可验证的物理信号（如阀线圈电压、气源压力表读数、开关触点通断）作为判断依据。1个复杂问题概要：多个基本事件在时间上高度耦合。具体问题：如某工位连续出现‘伺服脱扣’和‘安全继电器断开’两个基本事件，表面看是并列关系，实则后者是前者的连锁反应。解决思路：调取PLC周期扫描日志与安全控制器事件时序，按毫秒级时间戳比对信号变化先后顺序，确认因果链而非简单罗列。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>故障诊断与可靠性</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>故障根因分析</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>故障树拆解</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>请简述设备综合效率，也就是OEE，由哪三个核心要素组成？</t>
+          <t>产线优化与运维</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>OEE由可用率、性能率和合格率这三个核心要素组成。可用率反映设备实际运行时间占计划运行时间的比例；性能率反映设备在运行过程中实际产出速度与理论最大速度的匹配程度；合格率反映设备生产出的合格品数量占总产出数量的比例。</t>
+          <t>设备效率与数据分析</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>在产线日常运维中，自动化工程师常用三种方式获取这三个要素：一是通过PLC内置计时与脉冲采集实时统计停机与节拍，优势是响应快、无需额外硬件，但依赖程序逻辑完整性；二是部署边缘网关对接设备IO点与HMI操作日志，能自动归类停机原因，实施成本适中，但需协调不同品牌设备通信协议；三是结合视觉检测与扫码系统联动判定合格品，数据可信度高，但对现场光照、安装精度敏感。综合来看，第二种方式最常用——它在时效性、覆盖维度和落地可行性之间取得最佳平衡，既支持分钟级OEE刷新，又能支撑后续根因分析。</t>
+          <t>OEE与稼动率分析</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>1个异常情况概要：可用率突然下降但无明显报警。具体情况：PLC未触发故障信号，但设备频繁出现1–2分钟短暂停机。解决思路：调取边缘网关记录的IO状态序列，重点比对急停回路、安全门触点与复位按钮的毫秒级时序，排查人为误操作或安全继电器接触不良。1个复杂问题概要：同一型号多台设备OEE差异显著。具体问题：三台相同工位的装配机器人，可用率接近，但性能率与合格率呈现强负相关——性能高的反而合格率低。解决思路：同步采集各台机器人的伺服电流曲线、轨迹跟踪误差和末端力传感器数据，定位是否存在参数漂移导致的刚性过调，再结合工艺窗口校准而非单纯调速优化。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>产线优化与运维</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>设备效率与数据分析</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>OEE与稼动率分析</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>请简述什么是产线中的瓶颈工序。</t>
+          <t>产线优化与运维</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>瓶颈工序是指整条产线中节拍最慢、实际产出能力最低的工序，它直接决定了整条产线的最大理论产能，其他工序的运行节奏必须围绕它来匹配和调整。</t>
+          <t>产能与良率优化</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>在自动化工程师日常工作中，识别瓶颈工序通常采用三种主流方法：一是基于设备运行数据的节拍分析法，通过PLC采集各工位循环时间，统计长期稳定运行下的最小平均节拍，优势是客观可靠、可追溯，但需产线连续运行至少一个班次才能收敛；二是人机协同观察法，结合操作员反馈与现场计时，适合新线调试或柔性产线，响应快但主观性强；三是OEE分项拆解法，聚焦可用率、性能率和良品率三维度，定位低性能率或频繁停机的工位，覆盖全面但需要质量与设备数据联动。综合来看，节拍分析法最适合作为自动化工程师的首选手段，因为它直接对接PLC底层时序逻辑，与控制系统深度耦合，时效性与准确性兼顾。</t>
+          <t>瓶颈工序识别</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>1个异常情况概要：节拍数据短期波动掩盖真实瓶颈。具体情况：某装配工位因传感器偶发误触发导致PLC记录循环时间骤增，系统误判为瓶颈，而实际是信号干扰问题。解决思路：先隔离该工位输入信号，比对原始IO状态与HMI显示差异，确认是否为电气抗干扰不足所致，再针对性加装滤波或屏蔽措施。1个复杂问题概要：多品种共线生产下瓶颈动态漂移。具体问题：同一产线切换不同型号产品时，原非瓶颈工位因换型后夹具适配慢、参数重载耗时长，反而成为新瓶颈。解决思路：将换型动作分解为标准化子步骤，通过PLC程序预加载常用参数、设置并行准备逻辑，并在MES下发工单时同步推送最优节拍基准值，实现瓶颈预测与资源预调度。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>产线优化与运维</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>产能与良率优化</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>瓶颈工序识别</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>请简述什么是生产数据中的异常趋势。</t>
+          <t>智能制造改善</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>生产数据中的异常趋势，是指在连续采集的设备运行参数、工艺过程变量或质量检测结果中，出现偏离正常生产规律的持续性变化模式，这种变化不是瞬时扰动，而是具有时间延续性、方向性和可识别性的偏移或波动。</t>
+          <t>生产数据分析</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>在自动化工程师日常工作中，识别这类趋势主要依靠三种方法：一是基于历史基线的滑动窗口对比，响应快但对产线换型适应慢；二是多变量相关性分析，能捕捉跨设备耦合异常，但需要较完整的信号同步和标定；三是轻量级在线状态机建模，用有限状态迁移刻画典型工况，鲁棒性强且部署成本低。综合来看，第三种方法最适合产线现场——它不依赖大量历史数据，能嵌入PLC边缘侧实时运行，兼顾时效性与工程稳定性。</t>
+          <t>异常趋势识别</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>1个异常情况概要：注塑机保压压力曲线持续缓慢下降。具体情况：连续5模次以上保压峰值逐模降低0.8MPa以上，且无参数变更记录。解决思路：先锁定该机台对应温控与液压阀的实时反馈信号，比对伺服阀指令与实际阀位偏差，确认是否为比例阀卡滞或油温漂移导致执行衰减。1个复杂问题概要：多工位装配线中，某扭矩监测点趋势异常但相邻工位无同步变化。具体问题：仅第3工位螺栓拧紧曲线出现周期性超调，而第2、4工位数据正常，PLC程序版本与传感器型号均一致。解决思路：排查该工位专用IO模块的采样时钟抖动，检查其与主站同步机制是否因布线干扰发生微秒级失步，再验证扭矩传感器安装刚性是否因夹具松动引入谐振假象。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>智能制造改善</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>生产数据分析</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>异常趋势识别</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>请简述为什么保护接地回路必须保持连续、低阻抗，不能串联接入开关或熔断器。</t>
+          <t>电气控制基础</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>因为保护接地回路的作用是在设备发生绝缘失效、外壳带电时，为故障电流提供一条可靠通路，促使保护装置快速动作切断电源。只有回路连续且阻抗足够低，才能确保故障电流足够大、响应足够快，从而避免人员触电和设备起火风险。</t>
+          <t>电气原理识读</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>在自动化产线现场，常见做法有三种：一是采用专用黄绿双色多股铜导线全程压接，端子紧固并做防松标记；二是使用预制式接地汇流排，统一接入主接地端子；三是通过金属桥架或设备机柜本体作辅助等电位连接，但必须验证其电气连续性。第一种最可靠，抗振动和老化能力强；第二种便于后期扩展，但依赖安装精度；第三种成本低，但易因漆层、锈蚀或螺栓松动导致阻抗升高，需定期检测。综合来看，全程独立导线压接是当前主流产线首选方案。</t>
+          <t>接地与保护回路</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>1个异常情况概要：接地导线中间被无意剪断后用胶布缠绕恢复。具体情况：维修人员更换传感器时误伤接地线，临时包扎未做阻抗测试，导致某台PLC控制柜外壳在漏电时电压升至30伏以上。解决思路：建立接地线‘不可中断’作业红线，所有接地操作必须使用带力矩标识的压接端子，并在上电前用专用接地电阻测试仪实测回路阻值。1个复杂问题概要：多台变频器共用同一接地干线引发高频干扰与接地电位抬升。具体问题：伺服系统出现随机停机，示波器测得PE线上存在数安培的高频杂散电流。解决思路：实施‘一点接地+功能分区’策略，将安全保护接地与信号参考接地物理分离，关键设备单独敷设短直接地支线，避免形成接地环路。</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>电气控制基础</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>电气原理识读</t>
+          <t>自动化工程师</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>接地与保护回路</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>自动化工程师</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
